--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6237" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56AD1914-54E5-48D8-B105-B3432D430B08}"/>
+  <xr:revisionPtr revIDLastSave="6253" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7AD3822-0674-471E-8B83-585415A3AB1A}"/>
   <bookViews>
     <workbookView xWindow="10368" yWindow="1740" windowWidth="13908" windowHeight="9516" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -59,6 +59,9 @@
     <t>Credit Card</t>
   </si>
   <si>
+    <t>ATM</t>
+  </si>
+  <si>
     <t>TMT</t>
   </si>
   <si>
@@ -66,6 +69,9 @@
   </si>
   <si>
     <t>GFPT</t>
+  </si>
+  <si>
+    <t>SINGER</t>
   </si>
 </sst>
 </file>
@@ -77,7 +83,7 @@
     <numFmt numFmtId="188" formatCode="\฿#,##0.00"/>
     <numFmt numFmtId="189" formatCode="&quot;฿&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -132,6 +138,11 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -154,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -171,6 +182,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="189" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="188" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -509,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="11.42578125" style="2" customWidth="1"/>
@@ -567,73 +579,73 @@
       <c r="H2" s="8"/>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1">
-      <c r="A3" s="3">
-        <v>44925</v>
+      <c r="A3" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="B3" s="3">
-        <v>44931</v>
-      </c>
-      <c r="C3" s="4" t="s">
+        <v>44930</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="11">
-        <v>0</v>
-      </c>
-      <c r="E3" s="11">
-        <v>49390.36</v>
-      </c>
-      <c r="F3" s="6">
-        <f t="shared" ref="F3:F4" si="0">F2-D3+E3</f>
-        <v>263429.09000000125</v>
-      </c>
-      <c r="G3" s="7"/>
-      <c r="H3" s="8"/>
+      <c r="D3" s="9">
+        <v>1900</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0</v>
+      </c>
+      <c r="F3" s="16">
+        <f t="shared" ref="F3" si="0">F2-D3+E3</f>
+        <v>212138.73000000126</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1">
       <c r="A4" s="3">
         <v>44925</v>
       </c>
       <c r="B4" s="3">
-        <v>44931</v>
-      </c>
-      <c r="C4" s="8" t="s">
+        <v>44930</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="9">
-        <v>14.98</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0</v>
+      <c r="D4" s="11">
+        <v>0</v>
+      </c>
+      <c r="E4" s="11">
+        <v>49390.36</v>
       </c>
       <c r="F4" s="6">
-        <f t="shared" si="0"/>
-        <v>263414.11000000127</v>
-      </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
+        <f>F2-D4+E4</f>
+        <v>263429.09000000125</v>
+      </c>
+      <c r="G4" s="7"/>
+      <c r="H4" s="8"/>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1">
       <c r="A5" s="3">
-        <v>44929</v>
+        <v>44925</v>
       </c>
       <c r="B5" s="3">
-        <v>44931</v>
-      </c>
-      <c r="C5" s="4" t="s">
+        <v>44930</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="11">
-        <v>0</v>
-      </c>
-      <c r="E5" s="11">
-        <v>98032.38</v>
-      </c>
-      <c r="F5" s="6">
-        <f t="shared" ref="F5:F6" si="1">F4-D5+E5</f>
-        <v>361446.49000000127</v>
-      </c>
-      <c r="G5" s="7"/>
-      <c r="H5" s="8"/>
+      <c r="D5" s="9">
+        <v>14.98</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0</v>
+      </c>
+      <c r="F5" s="16">
+        <f t="shared" ref="F5" si="1">F4-D5+E5</f>
+        <v>263414.11000000127</v>
+      </c>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
       <c r="A6" s="3">
@@ -642,21 +654,90 @@
       <c r="B6" s="3">
         <v>44931</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="9">
+      <c r="C6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="11">
+        <v>0</v>
+      </c>
+      <c r="E6" s="11">
+        <v>98032.38</v>
+      </c>
+      <c r="F6" s="6">
+        <f t="shared" ref="F6:F7" si="2">F5-D6+E6</f>
+        <v>361446.49000000127</v>
+      </c>
+      <c r="G6" s="7"/>
+      <c r="H6" s="8"/>
+    </row>
+    <row r="7" spans="1:8" ht="15" customHeight="1">
+      <c r="A7" s="3">
+        <v>44929</v>
+      </c>
+      <c r="B7" s="3">
+        <v>44931</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="9">
         <v>14.98</v>
       </c>
-      <c r="E6" s="9">
-        <v>0</v>
-      </c>
-      <c r="F6" s="6">
-        <f t="shared" si="1"/>
+      <c r="E7" s="9">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6">
+        <f t="shared" si="2"/>
         <v>361431.51000000129</v>
       </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+    </row>
+    <row r="8" spans="1:8" ht="15" customHeight="1">
+      <c r="A8" s="3">
+        <v>44930</v>
+      </c>
+      <c r="B8" s="3">
+        <v>44932</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="11">
+        <v>99219.28</v>
+      </c>
+      <c r="E8" s="11">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6">
+        <f t="shared" ref="F8:F9" si="3">F7-D8+E8</f>
+        <v>262212.23000000126</v>
+      </c>
+      <c r="G8" s="7"/>
+      <c r="H8" s="8"/>
+    </row>
+    <row r="9" spans="1:8" ht="15" customHeight="1">
+      <c r="A9" s="3">
+        <v>44930</v>
+      </c>
+      <c r="B9" s="3">
+        <v>44932</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="9">
+        <v>14.98</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6">
+        <f t="shared" si="3"/>
+        <v>262197.25000000128</v>
+      </c>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6253" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7AD3822-0674-471E-8B83-585415A3AB1A}"/>
+  <xr:revisionPtr revIDLastSave="6259" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E729DF37-227B-4DF4-85F0-915DCF01547B}"/>
   <bookViews>
     <workbookView xWindow="10368" yWindow="1740" windowWidth="13908" windowHeight="9516" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t>SINGER</t>
+  </si>
+  <si>
+    <t>BANPU</t>
   </si>
 </sst>
 </file>
@@ -521,7 +524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="11.42578125" style="2" customWidth="1"/>
@@ -739,6 +742,52 @@
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
     </row>
+    <row r="10" spans="1:8" ht="15" customHeight="1">
+      <c r="A10" s="3">
+        <v>44932</v>
+      </c>
+      <c r="B10" s="3">
+        <v>44936</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="11">
+        <v>147926.92000000001</v>
+      </c>
+      <c r="E10" s="11">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6">
+        <f t="shared" ref="F10:F11" si="4">F9-D10+E10</f>
+        <v>114270.33000000127</v>
+      </c>
+      <c r="G10" s="7"/>
+      <c r="H10" s="8"/>
+    </row>
+    <row r="11" spans="1:8" ht="15" customHeight="1">
+      <c r="A11" s="3">
+        <v>44932</v>
+      </c>
+      <c r="B11" s="3">
+        <v>44936</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="9">
+        <v>14.98</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6">
+        <f t="shared" si="4"/>
+        <v>114255.35000000127</v>
+      </c>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6259" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E729DF37-227B-4DF4-85F0-915DCF01547B}"/>
+  <xr:revisionPtr revIDLastSave="6272" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09723208-20FC-42BB-8A7F-895AE30CFC48}"/>
   <bookViews>
     <workbookView xWindow="10368" yWindow="1740" windowWidth="13908" windowHeight="9516" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -524,7 +524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="11.42578125" style="2" customWidth="1"/>
@@ -575,7 +575,7 @@
       <c r="E2" s="9">
         <v>0</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="16">
         <v>214038.73000000126</v>
       </c>
       <c r="G2" s="10"/>
@@ -621,8 +621,8 @@
         <v>49390.36</v>
       </c>
       <c r="F4" s="6">
-        <f>F2-D4+E4</f>
-        <v>263429.09000000125</v>
+        <f>F3-D4+E4</f>
+        <v>261529.09000000125</v>
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="8"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="F5" s="16">
         <f t="shared" ref="F5" si="1">F4-D5+E5</f>
-        <v>263414.11000000127</v>
+        <v>261514.11000000124</v>
       </c>
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
@@ -668,7 +668,7 @@
       </c>
       <c r="F6" s="6">
         <f t="shared" ref="F6:F7" si="2">F5-D6+E6</f>
-        <v>361446.49000000127</v>
+        <v>359546.49000000127</v>
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="8"/>
@@ -689,9 +689,9 @@
       <c r="E7" s="9">
         <v>0</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="16">
         <f t="shared" si="2"/>
-        <v>361431.51000000129</v>
+        <v>359531.51000000129</v>
       </c>
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
@@ -714,7 +714,7 @@
       </c>
       <c r="F8" s="6">
         <f t="shared" ref="F8:F9" si="3">F7-D8+E8</f>
-        <v>262212.23000000126</v>
+        <v>260312.23000000129</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="8"/>
@@ -735,9 +735,9 @@
       <c r="E9" s="9">
         <v>0</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="16">
         <f t="shared" si="3"/>
-        <v>262197.25000000128</v>
+        <v>260297.25000000128</v>
       </c>
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
@@ -759,8 +759,8 @@
         <v>0</v>
       </c>
       <c r="F10" s="6">
-        <f t="shared" ref="F10:F11" si="4">F9-D10+E10</f>
-        <v>114270.33000000127</v>
+        <f t="shared" ref="F10:F12" si="4">F9-D10+E10</f>
+        <v>112370.33000000127</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="8"/>
@@ -783,10 +783,79 @@
       </c>
       <c r="F11" s="6">
         <f t="shared" si="4"/>
-        <v>114255.35000000127</v>
+        <v>112355.35000000127</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
+    </row>
+    <row r="12" spans="1:8" ht="15" customHeight="1">
+      <c r="A12" s="3">
+        <v>44935</v>
+      </c>
+      <c r="B12" s="3">
+        <v>44937</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="11">
+        <v>0</v>
+      </c>
+      <c r="E12" s="11">
+        <v>125720.92</v>
+      </c>
+      <c r="F12" s="6">
+        <f t="shared" si="4"/>
+        <v>238076.27000000127</v>
+      </c>
+      <c r="G12" s="7"/>
+      <c r="H12" s="8"/>
+    </row>
+    <row r="13" spans="1:8" ht="15" customHeight="1">
+      <c r="A13" s="3">
+        <v>44935</v>
+      </c>
+      <c r="B13" s="3">
+        <v>44937</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="11">
+        <v>0</v>
+      </c>
+      <c r="E13" s="11">
+        <v>105066.77</v>
+      </c>
+      <c r="F13" s="6">
+        <f t="shared" ref="F13:F14" si="5">F12-D13+E13</f>
+        <v>343143.04000000126</v>
+      </c>
+      <c r="G13" s="7"/>
+      <c r="H13" s="8"/>
+    </row>
+    <row r="14" spans="1:8" ht="15" customHeight="1">
+      <c r="A14" s="3">
+        <v>44935</v>
+      </c>
+      <c r="B14" s="3">
+        <v>44937</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="9">
+        <v>14.98</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0</v>
+      </c>
+      <c r="F14" s="6">
+        <f t="shared" si="5"/>
+        <v>343128.06000000128</v>
+      </c>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26111"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6272" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09723208-20FC-42BB-8A7F-895AE30CFC48}"/>
+  <xr:revisionPtr revIDLastSave="6288" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9137E5C4-FE3E-48AA-BAC3-53A8B05F287B}"/>
   <bookViews>
     <workbookView xWindow="10368" yWindow="1740" windowWidth="13908" windowHeight="9516" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -75,6 +75,12 @@
   </si>
   <si>
     <t>BANPU</t>
+  </si>
+  <si>
+    <t>PTTGC</t>
+  </si>
+  <si>
+    <t>GVREIT</t>
   </si>
 </sst>
 </file>
@@ -524,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="11.42578125" style="2" customWidth="1"/>
@@ -857,6 +863,121 @@
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
     </row>
+    <row r="15" spans="1:8" ht="15" customHeight="1">
+      <c r="A15" s="3">
+        <v>44943</v>
+      </c>
+      <c r="B15" s="3">
+        <v>44945</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="11">
+        <v>0</v>
+      </c>
+      <c r="E15" s="11">
+        <v>151912.78</v>
+      </c>
+      <c r="F15" s="6">
+        <f t="shared" ref="F15" si="6">F14-D15+E15</f>
+        <v>495040.84000000125</v>
+      </c>
+      <c r="G15" s="7"/>
+      <c r="H15" s="8"/>
+    </row>
+    <row r="16" spans="1:8" ht="15" customHeight="1">
+      <c r="A16" s="3">
+        <v>44943</v>
+      </c>
+      <c r="B16" s="3">
+        <v>44945</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="11">
+        <v>89197.13</v>
+      </c>
+      <c r="E16" s="11">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6">
+        <f t="shared" ref="F16:F17" si="7">F15-D16+E16</f>
+        <v>405843.71000000124</v>
+      </c>
+      <c r="G16" s="7"/>
+      <c r="H16" s="8"/>
+    </row>
+    <row r="17" spans="1:8" ht="15" customHeight="1">
+      <c r="A17" s="3">
+        <v>44943</v>
+      </c>
+      <c r="B17" s="3">
+        <v>44945</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="9">
+        <v>14.98</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0</v>
+      </c>
+      <c r="F17" s="6">
+        <f t="shared" si="7"/>
+        <v>405828.73000000126</v>
+      </c>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+    </row>
+    <row r="18" spans="1:8" ht="15" customHeight="1">
+      <c r="A18" s="3">
+        <v>44944</v>
+      </c>
+      <c r="B18" s="3">
+        <v>44946</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="11">
+        <v>89197.13</v>
+      </c>
+      <c r="E18" s="11">
+        <v>0</v>
+      </c>
+      <c r="F18" s="6">
+        <f t="shared" ref="F18:F19" si="8">F17-D18+E18</f>
+        <v>316631.60000000126</v>
+      </c>
+      <c r="G18" s="7"/>
+      <c r="H18" s="8"/>
+    </row>
+    <row r="19" spans="1:8" ht="15" customHeight="1">
+      <c r="A19" s="3">
+        <v>44944</v>
+      </c>
+      <c r="B19" s="3">
+        <v>44946</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="9">
+        <v>14.98</v>
+      </c>
+      <c r="E19" s="9">
+        <v>0</v>
+      </c>
+      <c r="F19" s="6">
+        <f t="shared" si="8"/>
+        <v>316616.62000000128</v>
+      </c>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6288" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9137E5C4-FE3E-48AA-BAC3-53A8B05F287B}"/>
+  <xr:revisionPtr revIDLastSave="6332" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E20A9FC4-03C9-4D5A-B130-675D68A44E7B}"/>
   <bookViews>
     <workbookView xWindow="10368" yWindow="1740" windowWidth="13908" windowHeight="9516" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="20">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -77,10 +77,22 @@
     <t>BANPU</t>
   </si>
   <si>
+    <t>SMS</t>
+  </si>
+  <si>
+    <t>???</t>
+  </si>
+  <si>
+    <t>SSF</t>
+  </si>
+  <si>
     <t>PTTGC</t>
   </si>
   <si>
     <t>GVREIT</t>
+  </si>
+  <si>
+    <t>STA</t>
   </si>
 </sst>
 </file>
@@ -530,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="11.42578125" style="2" customWidth="1"/>
@@ -787,7 +799,7 @@
       <c r="E11" s="9">
         <v>0</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="16">
         <f t="shared" si="4"/>
         <v>112355.35000000127</v>
       </c>
@@ -856,7 +868,7 @@
       <c r="E14" s="9">
         <v>0</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="16">
         <f t="shared" si="5"/>
         <v>343128.06000000128</v>
       </c>
@@ -864,119 +876,280 @@
       <c r="H14" s="10"/>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1">
-      <c r="A15" s="3">
-        <v>44943</v>
+      <c r="A15" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="B15" s="3">
-        <v>44945</v>
-      </c>
-      <c r="C15" s="4" t="s">
+        <v>44940</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="11">
-        <v>0</v>
-      </c>
-      <c r="E15" s="11">
-        <v>151912.78</v>
-      </c>
-      <c r="F15" s="6">
+      <c r="D15" s="9">
+        <v>20</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0</v>
+      </c>
+      <c r="F15" s="16">
         <f t="shared" ref="F15" si="6">F14-D15+E15</f>
-        <v>495040.84000000125</v>
-      </c>
-      <c r="G15" s="7"/>
-      <c r="H15" s="8"/>
+        <v>343108.06000000128</v>
+      </c>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1">
-      <c r="A16" s="3">
-        <v>44943</v>
+      <c r="A16" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="B16" s="3">
-        <v>44945</v>
-      </c>
-      <c r="C16" s="4" t="s">
+        <v>44941</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="11">
-        <v>89197.13</v>
-      </c>
-      <c r="E16" s="11">
-        <v>0</v>
-      </c>
-      <c r="F16" s="6">
-        <f t="shared" ref="F16:F17" si="7">F15-D16+E16</f>
-        <v>405843.71000000124</v>
-      </c>
-      <c r="G16" s="7"/>
-      <c r="H16" s="8"/>
+      <c r="D16" s="9">
+        <v>225</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0</v>
+      </c>
+      <c r="F16" s="16">
+        <f>F15-D16+E16</f>
+        <v>342883.06000000128</v>
+      </c>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1">
-      <c r="A17" s="3">
-        <v>44943</v>
+      <c r="A17" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="B17" s="3">
-        <v>44945</v>
+        <v>44942</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D17" s="9">
-        <v>14.98</v>
+        <v>240</v>
       </c>
       <c r="E17" s="9">
         <v>0</v>
       </c>
-      <c r="F17" s="6">
-        <f t="shared" si="7"/>
-        <v>405828.73000000126</v>
+      <c r="F17" s="16">
+        <f>F16-D17+E17</f>
+        <v>342643.06000000128</v>
       </c>
       <c r="G17" s="10"/>
       <c r="H17" s="10"/>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1">
-      <c r="A18" s="3">
-        <v>44944</v>
+      <c r="A18" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="B18" s="3">
-        <v>44946</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="11">
-        <v>89197.13</v>
-      </c>
-      <c r="E18" s="11">
-        <v>0</v>
-      </c>
-      <c r="F18" s="6">
-        <f t="shared" ref="F18:F19" si="8">F17-D18+E18</f>
-        <v>316631.60000000126</v>
-      </c>
-      <c r="G18" s="7"/>
-      <c r="H18" s="8"/>
+        <v>44945</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="9">
+        <v>0</v>
+      </c>
+      <c r="E18" s="9">
+        <v>304081.40000000002</v>
+      </c>
+      <c r="F18" s="16">
+        <f t="shared" ref="F18:F26" si="7">F17-D18+E18</f>
+        <v>646724.46000000136</v>
+      </c>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1">
       <c r="A19" s="3">
+        <v>44943</v>
+      </c>
+      <c r="B19" s="3">
+        <v>44945</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="11">
+        <v>0</v>
+      </c>
+      <c r="E19" s="11">
+        <v>151912.78</v>
+      </c>
+      <c r="F19" s="6">
+        <f t="shared" si="7"/>
+        <v>798637.24000000139</v>
+      </c>
+      <c r="G19" s="7"/>
+      <c r="H19" s="8"/>
+    </row>
+    <row r="20" spans="1:8" ht="15" customHeight="1">
+      <c r="A20" s="3">
+        <v>44943</v>
+      </c>
+      <c r="B20" s="3">
+        <v>44945</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="11">
+        <v>89197.13</v>
+      </c>
+      <c r="E20" s="11">
+        <v>0</v>
+      </c>
+      <c r="F20" s="6">
+        <f t="shared" si="7"/>
+        <v>709440.11000000138</v>
+      </c>
+      <c r="G20" s="7"/>
+      <c r="H20" s="8"/>
+    </row>
+    <row r="21" spans="1:8" ht="15" customHeight="1">
+      <c r="A21" s="3">
+        <v>44943</v>
+      </c>
+      <c r="B21" s="3">
+        <v>44945</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="9">
+        <v>14.98</v>
+      </c>
+      <c r="E21" s="9">
+        <v>0</v>
+      </c>
+      <c r="F21" s="16">
+        <f t="shared" si="7"/>
+        <v>709425.1300000014</v>
+      </c>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+    </row>
+    <row r="22" spans="1:8" ht="15" customHeight="1">
+      <c r="A22" s="3">
         <v>44944</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B22" s="3">
         <v>44946</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="11">
+        <v>89197.13</v>
+      </c>
+      <c r="E22" s="11">
+        <v>0</v>
+      </c>
+      <c r="F22" s="6">
+        <f t="shared" si="7"/>
+        <v>620228.0000000014</v>
+      </c>
+      <c r="G22" s="7"/>
+      <c r="H22" s="8"/>
+    </row>
+    <row r="23" spans="1:8" ht="15" customHeight="1">
+      <c r="A23" s="3">
+        <v>44944</v>
+      </c>
+      <c r="B23" s="3">
+        <v>44946</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D23" s="9">
         <v>14.98</v>
       </c>
-      <c r="E19" s="9">
-        <v>0</v>
-      </c>
-      <c r="F19" s="6">
-        <f t="shared" si="8"/>
-        <v>316616.62000000128</v>
-      </c>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
+      <c r="E23" s="9">
+        <v>0</v>
+      </c>
+      <c r="F23" s="6">
+        <f t="shared" si="7"/>
+        <v>620213.02000000142</v>
+      </c>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+    </row>
+    <row r="24" spans="1:8" ht="15" customHeight="1">
+      <c r="A24" s="3">
+        <v>44945</v>
+      </c>
+      <c r="B24" s="3">
+        <v>45100</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="11">
+        <v>101023.27</v>
+      </c>
+      <c r="E24" s="11">
+        <v>0</v>
+      </c>
+      <c r="F24" s="6">
+        <f t="shared" si="7"/>
+        <v>519189.7500000014</v>
+      </c>
+      <c r="G24" s="7"/>
+      <c r="H24" s="8"/>
+    </row>
+    <row r="25" spans="1:8" ht="15" customHeight="1">
+      <c r="A25" s="3">
+        <v>44945</v>
+      </c>
+      <c r="B25" s="3">
+        <v>45100</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="11">
+        <v>0</v>
+      </c>
+      <c r="E25" s="11">
+        <v>52882.61</v>
+      </c>
+      <c r="F25" s="6">
+        <f t="shared" si="7"/>
+        <v>572072.36000000138</v>
+      </c>
+      <c r="G25" s="7"/>
+      <c r="H25" s="8"/>
+    </row>
+    <row r="26" spans="1:8" ht="15" customHeight="1">
+      <c r="A26" s="3">
+        <v>44945</v>
+      </c>
+      <c r="B26" s="3">
+        <v>45100</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="9">
+        <v>14.98</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0</v>
+      </c>
+      <c r="F26" s="6">
+        <f t="shared" si="7"/>
+        <v>572057.3800000014</v>
+      </c>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6332" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E20A9FC4-03C9-4D5A-B130-675D68A44E7B}"/>
+  <xr:revisionPtr revIDLastSave="6340" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9E4D0CD-48EE-4C9A-926C-BB8DDD227F43}"/>
   <bookViews>
     <workbookView xWindow="10368" yWindow="1740" windowWidth="13908" windowHeight="9516" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="21">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>STA</t>
+  </si>
+  <si>
+    <t>JMT</t>
   </si>
 </sst>
 </file>
@@ -542,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="11.42578125" style="2" customWidth="1"/>
@@ -1075,7 +1078,7 @@
       <c r="E23" s="9">
         <v>0</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="16">
         <f t="shared" si="7"/>
         <v>620213.02000000142</v>
       </c>
@@ -1150,6 +1153,52 @@
       </c>
       <c r="G26" s="10"/>
       <c r="H26" s="10"/>
+    </row>
+    <row r="27" spans="1:8" ht="15" customHeight="1">
+      <c r="A27" s="3">
+        <v>44946</v>
+      </c>
+      <c r="B27" s="3">
+        <v>44950</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="11">
+        <v>142514.95000000001</v>
+      </c>
+      <c r="E27" s="11">
+        <v>0</v>
+      </c>
+      <c r="F27" s="6">
+        <f t="shared" ref="F27:F28" si="8">F26-D27+E27</f>
+        <v>429542.43000000139</v>
+      </c>
+      <c r="G27" s="7"/>
+      <c r="H27" s="8"/>
+    </row>
+    <row r="28" spans="1:8" ht="15" customHeight="1">
+      <c r="A28" s="3">
+        <v>44946</v>
+      </c>
+      <c r="B28" s="3">
+        <v>44950</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="9">
+        <v>14.98</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0</v>
+      </c>
+      <c r="F28" s="6">
+        <f t="shared" si="8"/>
+        <v>429527.45000000141</v>
+      </c>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6340" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9E4D0CD-48EE-4C9A-926C-BB8DDD227F43}"/>
+  <xr:revisionPtr revIDLastSave="6378" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3D11E97-5D30-4789-B7C1-62705D3902C3}"/>
   <bookViews>
     <workbookView xWindow="10368" yWindow="1740" windowWidth="13908" windowHeight="9516" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="23">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -96,6 +96,12 @@
   </si>
   <si>
     <t>JMT</t>
+  </si>
+  <si>
+    <t>MAKRO</t>
+  </si>
+  <si>
+    <t>CPNREIT</t>
   </si>
 </sst>
 </file>
@@ -545,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="11.42578125" style="2" customWidth="1"/>
@@ -1171,7 +1177,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="6">
-        <f t="shared" ref="F27:F28" si="8">F26-D27+E27</f>
+        <f t="shared" ref="F27:F30" si="8">F26-D27+E27</f>
         <v>429542.43000000139</v>
       </c>
       <c r="G27" s="7"/>
@@ -1199,6 +1205,98 @@
       </c>
       <c r="G28" s="10"/>
       <c r="H28" s="10"/>
+    </row>
+    <row r="29" spans="1:8" ht="15" customHeight="1">
+      <c r="A29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="3">
+        <v>44950</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="9">
+        <v>29500</v>
+      </c>
+      <c r="E29" s="9">
+        <v>0</v>
+      </c>
+      <c r="F29" s="6">
+        <f t="shared" si="8"/>
+        <v>400027.45000000141</v>
+      </c>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+    </row>
+    <row r="30" spans="1:8" ht="15" customHeight="1">
+      <c r="A30" s="3">
+        <v>44950</v>
+      </c>
+      <c r="B30" s="3">
+        <v>44952</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" s="11">
+        <v>0</v>
+      </c>
+      <c r="E30" s="11">
+        <v>318044</v>
+      </c>
+      <c r="F30" s="6">
+        <f t="shared" si="8"/>
+        <v>718071.45000000135</v>
+      </c>
+      <c r="G30" s="7"/>
+      <c r="H30" s="8"/>
+    </row>
+    <row r="31" spans="1:8" ht="15" customHeight="1">
+      <c r="A31" s="3">
+        <v>44950</v>
+      </c>
+      <c r="B31" s="3">
+        <v>44952</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31" s="11">
+        <v>195431.91</v>
+      </c>
+      <c r="E31" s="11">
+        <v>0</v>
+      </c>
+      <c r="F31" s="6">
+        <f t="shared" ref="F31:F32" si="9">F30-D31+E31</f>
+        <v>522639.54000000132</v>
+      </c>
+      <c r="G31" s="7"/>
+      <c r="H31" s="8"/>
+    </row>
+    <row r="32" spans="1:8" ht="15" customHeight="1">
+      <c r="A32" s="3">
+        <v>44950</v>
+      </c>
+      <c r="B32" s="3">
+        <v>44952</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" s="9">
+        <v>14.98</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0</v>
+      </c>
+      <c r="F32" s="6">
+        <f t="shared" si="9"/>
+        <v>522624.56000000134</v>
+      </c>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26111"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26124"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6378" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3D11E97-5D30-4789-B7C1-62705D3902C3}"/>
+  <xr:revisionPtr revIDLastSave="6405" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28E1F7EB-E669-4DC0-9BEE-6EF384EC6D18}"/>
   <bookViews>
     <workbookView xWindow="10368" yWindow="1740" windowWidth="13908" windowHeight="9516" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -98,10 +98,16 @@
     <t>JMT</t>
   </si>
   <si>
+    <t>Tax Refund</t>
+  </si>
+  <si>
     <t>MAKRO</t>
   </si>
   <si>
     <t>CPNREIT</t>
+  </si>
+  <si>
+    <t>IVL</t>
   </si>
 </sst>
 </file>
@@ -551,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="11.42578125" style="2" customWidth="1"/>
@@ -1177,7 +1183,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="6">
-        <f t="shared" ref="F27:F30" si="8">F26-D27+E27</f>
+        <f t="shared" ref="F27:F29" si="8">F26-D27+E27</f>
         <v>429542.43000000139</v>
       </c>
       <c r="G27" s="7"/>
@@ -1230,27 +1236,27 @@
       <c r="H29" s="10"/>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1">
-      <c r="A30" s="3">
-        <v>44950</v>
+      <c r="A30" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="B30" s="3">
-        <v>44952</v>
-      </c>
-      <c r="C30" s="4" t="s">
+        <v>44951</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D30" s="11">
-        <v>0</v>
-      </c>
-      <c r="E30" s="11">
-        <v>318044</v>
+      <c r="D30" s="9">
+        <v>0</v>
+      </c>
+      <c r="E30" s="9">
+        <v>102052.5</v>
       </c>
       <c r="F30" s="6">
-        <f t="shared" si="8"/>
-        <v>718071.45000000135</v>
-      </c>
-      <c r="G30" s="7"/>
-      <c r="H30" s="8"/>
+        <f t="shared" ref="F30:F36" si="9">F29-D30+E30</f>
+        <v>502079.95000000141</v>
+      </c>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1">
       <c r="A31" s="3">
@@ -1263,14 +1269,14 @@
         <v>22</v>
       </c>
       <c r="D31" s="11">
-        <v>195431.91</v>
+        <v>0</v>
       </c>
       <c r="E31" s="11">
-        <v>0</v>
+        <v>318044</v>
       </c>
       <c r="F31" s="6">
-        <f t="shared" ref="F31:F32" si="9">F30-D31+E31</f>
-        <v>522639.54000000132</v>
+        <f t="shared" si="9"/>
+        <v>820123.95000000135</v>
       </c>
       <c r="G31" s="7"/>
       <c r="H31" s="8"/>
@@ -1282,21 +1288,182 @@
       <c r="B32" s="3">
         <v>44952</v>
       </c>
-      <c r="C32" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D32" s="9">
-        <v>14.98</v>
-      </c>
-      <c r="E32" s="9">
+      <c r="C32" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" s="11">
+        <v>195431.91</v>
+      </c>
+      <c r="E32" s="11">
         <v>0</v>
       </c>
       <c r="F32" s="6">
         <f t="shared" si="9"/>
-        <v>522624.56000000134</v>
-      </c>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
+        <v>624692.04000000132</v>
+      </c>
+      <c r="G32" s="7"/>
+      <c r="H32" s="8"/>
+    </row>
+    <row r="33" spans="1:8" ht="15" customHeight="1">
+      <c r="A33" s="3">
+        <v>44950</v>
+      </c>
+      <c r="B33" s="3">
+        <v>44952</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" s="9">
+        <v>14.98</v>
+      </c>
+      <c r="E33" s="9">
+        <v>0</v>
+      </c>
+      <c r="F33" s="6">
+        <f t="shared" si="9"/>
+        <v>624677.06000000134</v>
+      </c>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+    </row>
+    <row r="34" spans="1:8" ht="15" customHeight="1">
+      <c r="A34" s="3">
+        <v>44951</v>
+      </c>
+      <c r="B34" s="3">
+        <v>44953</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="11">
+        <v>0</v>
+      </c>
+      <c r="E34" s="11">
+        <v>53381.5</v>
+      </c>
+      <c r="F34" s="6">
+        <f t="shared" si="9"/>
+        <v>678058.56000000134</v>
+      </c>
+      <c r="G34" s="7"/>
+      <c r="H34" s="8"/>
+    </row>
+    <row r="35" spans="1:8" ht="15" customHeight="1">
+      <c r="A35" s="3">
+        <v>44951</v>
+      </c>
+      <c r="B35" s="3">
+        <v>44953</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="11">
+        <v>0</v>
+      </c>
+      <c r="E35" s="11">
+        <v>54628.74</v>
+      </c>
+      <c r="F35" s="6">
+        <f t="shared" si="9"/>
+        <v>732687.30000000133</v>
+      </c>
+      <c r="G35" s="7"/>
+      <c r="H35" s="8"/>
+    </row>
+    <row r="36" spans="1:8" ht="15" customHeight="1">
+      <c r="A36" s="3">
+        <v>44951</v>
+      </c>
+      <c r="B36" s="3">
+        <v>44953</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" s="9">
+        <v>14.98</v>
+      </c>
+      <c r="E36" s="9">
+        <v>0</v>
+      </c>
+      <c r="F36" s="6">
+        <f t="shared" si="9"/>
+        <v>732672.32000000135</v>
+      </c>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+    </row>
+    <row r="37" spans="1:8" ht="15" customHeight="1">
+      <c r="A37" s="3">
+        <v>44952</v>
+      </c>
+      <c r="B37" s="3">
+        <v>44956</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" s="11">
+        <v>140710.97</v>
+      </c>
+      <c r="E37" s="11">
+        <v>0</v>
+      </c>
+      <c r="F37" s="6">
+        <f t="shared" ref="F37" si="10">F36-D37+E37</f>
+        <v>591961.35000000137</v>
+      </c>
+      <c r="G37" s="7"/>
+      <c r="H37" s="8"/>
+    </row>
+    <row r="38" spans="1:8" ht="15" customHeight="1">
+      <c r="A38" s="3">
+        <v>44952</v>
+      </c>
+      <c r="B38" s="3">
+        <v>44956</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D38" s="11">
+        <v>96212.63</v>
+      </c>
+      <c r="E38" s="11">
+        <v>0</v>
+      </c>
+      <c r="F38" s="6">
+        <f t="shared" ref="F38:F39" si="11">F37-D38+E38</f>
+        <v>495748.72000000137</v>
+      </c>
+      <c r="G38" s="7"/>
+      <c r="H38" s="8"/>
+    </row>
+    <row r="39" spans="1:8" ht="15" customHeight="1">
+      <c r="A39" s="3">
+        <v>44952</v>
+      </c>
+      <c r="B39" s="3">
+        <v>44956</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" s="9">
+        <v>14.98</v>
+      </c>
+      <c r="E39" s="9">
+        <v>0</v>
+      </c>
+      <c r="F39" s="6">
+        <f t="shared" si="11"/>
+        <v>495733.74000000139</v>
+      </c>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6405" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28E1F7EB-E669-4DC0-9BEE-6EF384EC6D18}"/>
+  <xr:revisionPtr revIDLastSave="6407" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F58A96EE-5E9F-4300-A0F9-90411BFF5B46}"/>
   <bookViews>
     <workbookView xWindow="10368" yWindow="1740" windowWidth="13908" windowHeight="9516" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6407" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F58A96EE-5E9F-4300-A0F9-90411BFF5B46}"/>
+  <xr:revisionPtr revIDLastSave="6424" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F7EB1B4-10AF-4CF2-B9A3-E2B079700AFC}"/>
   <bookViews>
     <workbookView xWindow="10368" yWindow="1740" windowWidth="13908" windowHeight="9516" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="26">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>IVL</t>
+  </si>
+  <si>
+    <t>WHAIR</t>
   </si>
 </sst>
 </file>
@@ -557,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="11.42578125" style="2" customWidth="1"/>
@@ -1389,7 +1392,7 @@
       <c r="E36" s="9">
         <v>0</v>
       </c>
-      <c r="F36" s="6">
+      <c r="F36" s="16">
         <f t="shared" si="9"/>
         <v>732672.32000000135</v>
       </c>
@@ -1464,6 +1467,121 @@
       </c>
       <c r="G39" s="10"/>
       <c r="H39" s="10"/>
+    </row>
+    <row r="40" spans="1:8" ht="15" customHeight="1">
+      <c r="A40" s="3">
+        <v>44956</v>
+      </c>
+      <c r="B40" s="3">
+        <v>44958</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D40" s="11">
+        <v>77170.55</v>
+      </c>
+      <c r="E40" s="11">
+        <v>0</v>
+      </c>
+      <c r="F40" s="6">
+        <f t="shared" ref="F40" si="12">F39-D40+E40</f>
+        <v>418563.1900000014</v>
+      </c>
+      <c r="G40" s="7"/>
+      <c r="H40" s="8"/>
+    </row>
+    <row r="41" spans="1:8" ht="15" customHeight="1">
+      <c r="A41" s="3">
+        <v>44956</v>
+      </c>
+      <c r="B41" s="3">
+        <v>44958</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D41" s="11">
+        <v>77170.55</v>
+      </c>
+      <c r="E41" s="11">
+        <v>0</v>
+      </c>
+      <c r="F41" s="6">
+        <f t="shared" ref="F41" si="13">F40-D41+E41</f>
+        <v>341392.64000000141</v>
+      </c>
+      <c r="G41" s="7"/>
+      <c r="H41" s="8"/>
+    </row>
+    <row r="42" spans="1:8" ht="15" customHeight="1">
+      <c r="A42" s="3">
+        <v>44956</v>
+      </c>
+      <c r="B42" s="3">
+        <v>44958</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" s="11">
+        <v>47805.65</v>
+      </c>
+      <c r="E42" s="11">
+        <v>0</v>
+      </c>
+      <c r="F42" s="6">
+        <f t="shared" ref="F42:F44" si="14">F41-D42+E42</f>
+        <v>293586.99000000139</v>
+      </c>
+      <c r="G42" s="7"/>
+      <c r="H42" s="8"/>
+    </row>
+    <row r="43" spans="1:8" ht="15" customHeight="1">
+      <c r="A43" s="3">
+        <v>44956</v>
+      </c>
+      <c r="B43" s="3">
+        <v>44958</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D43" s="11">
+        <v>0</v>
+      </c>
+      <c r="E43" s="11">
+        <v>77827.240000000005</v>
+      </c>
+      <c r="F43" s="6">
+        <f t="shared" si="14"/>
+        <v>371414.23000000138</v>
+      </c>
+      <c r="G43" s="7"/>
+      <c r="H43" s="8"/>
+    </row>
+    <row r="44" spans="1:8" ht="15" customHeight="1">
+      <c r="A44" s="3">
+        <v>44956</v>
+      </c>
+      <c r="B44" s="3">
+        <v>44958</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="9">
+        <v>14.98</v>
+      </c>
+      <c r="E44" s="9">
+        <v>0</v>
+      </c>
+      <c r="F44" s="6">
+        <f t="shared" si="14"/>
+        <v>371399.2500000014</v>
+      </c>
+      <c r="G44" s="10"/>
+      <c r="H44" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26124"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26129"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6424" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F7EB1B4-10AF-4CF2-B9A3-E2B079700AFC}"/>
+  <xr:revisionPtr revIDLastSave="6435" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{477F9D67-AEC6-4840-BCF8-DD3FB874CC14}"/>
   <bookViews>
     <workbookView xWindow="10368" yWindow="1740" windowWidth="13908" windowHeight="9516" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="27">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -111,6 +111,9 @@
   </si>
   <si>
     <t>WHAIR</t>
+  </si>
+  <si>
+    <t>KCE</t>
   </si>
 </sst>
 </file>
@@ -560,7 +563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="11.42578125" style="2" customWidth="1"/>
@@ -1583,6 +1586,75 @@
       <c r="G44" s="10"/>
       <c r="H44" s="10"/>
     </row>
+    <row r="45" spans="1:8" ht="15" customHeight="1">
+      <c r="A45" s="3">
+        <v>44957</v>
+      </c>
+      <c r="B45" s="3">
+        <v>44959</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D45" s="11">
+        <v>0</v>
+      </c>
+      <c r="E45" s="11">
+        <v>53630.95</v>
+      </c>
+      <c r="F45" s="6">
+        <f t="shared" ref="F45" si="15">F44-D45+E45</f>
+        <v>425030.20000000141</v>
+      </c>
+      <c r="G45" s="7"/>
+      <c r="H45" s="8"/>
+    </row>
+    <row r="46" spans="1:8" ht="15" customHeight="1">
+      <c r="A46" s="3">
+        <v>44957</v>
+      </c>
+      <c r="B46" s="3">
+        <v>44959</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="11">
+        <v>68551.5</v>
+      </c>
+      <c r="E46" s="11">
+        <v>0</v>
+      </c>
+      <c r="F46" s="6">
+        <f t="shared" ref="F46:F47" si="16">F45-D46+E46</f>
+        <v>356478.70000000141</v>
+      </c>
+      <c r="G46" s="7"/>
+      <c r="H46" s="8"/>
+    </row>
+    <row r="47" spans="1:8" ht="15" customHeight="1">
+      <c r="A47" s="3">
+        <v>44957</v>
+      </c>
+      <c r="B47" s="3">
+        <v>44959</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" s="9">
+        <v>14.98</v>
+      </c>
+      <c r="E47" s="9">
+        <v>0</v>
+      </c>
+      <c r="F47" s="6">
+        <f t="shared" si="16"/>
+        <v>356463.72000000143</v>
+      </c>
+      <c r="G47" s="10"/>
+      <c r="H47" s="10"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6435" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{477F9D67-AEC6-4840-BCF8-DD3FB874CC14}"/>
+  <xr:revisionPtr revIDLastSave="6457" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0837A1ED-6713-4E6E-915A-18753C7CA42E}"/>
   <bookViews>
     <workbookView xWindow="10368" yWindow="1740" windowWidth="13908" windowHeight="9516" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="28">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -114,6 +114,9 @@
   </si>
   <si>
     <t>KCE</t>
+  </si>
+  <si>
+    <t>RCL</t>
   </si>
 </sst>
 </file>
@@ -563,7 +566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="11.42578125" style="2" customWidth="1"/>
@@ -1442,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="6">
-        <f t="shared" ref="F38:F39" si="11">F37-D38+E38</f>
+        <f t="shared" ref="F38:F53" si="11">F37-D38+E38</f>
         <v>495748.72000000137</v>
       </c>
       <c r="G38" s="7"/>
@@ -1472,27 +1475,27 @@
       <c r="H39" s="10"/>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1">
-      <c r="A40" s="3">
-        <v>44956</v>
+      <c r="A40" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="B40" s="3">
-        <v>44958</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D40" s="11">
-        <v>77170.55</v>
-      </c>
-      <c r="E40" s="11">
+        <v>44957</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="9">
+        <v>27200</v>
+      </c>
+      <c r="E40" s="9">
         <v>0</v>
       </c>
       <c r="F40" s="6">
-        <f t="shared" ref="F40" si="12">F39-D40+E40</f>
-        <v>418563.1900000014</v>
-      </c>
-      <c r="G40" s="7"/>
-      <c r="H40" s="8"/>
+        <f t="shared" si="11"/>
+        <v>468533.74000000139</v>
+      </c>
+      <c r="G40" s="10"/>
+      <c r="H40" s="10"/>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1">
       <c r="A41" s="3">
@@ -1511,8 +1514,8 @@
         <v>0</v>
       </c>
       <c r="F41" s="6">
-        <f t="shared" ref="F41" si="13">F40-D41+E41</f>
-        <v>341392.64000000141</v>
+        <f t="shared" si="11"/>
+        <v>391363.1900000014</v>
       </c>
       <c r="G41" s="7"/>
       <c r="H41" s="8"/>
@@ -1525,17 +1528,17 @@
         <v>44958</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D42" s="11">
-        <v>47805.65</v>
+        <v>77170.55</v>
       </c>
       <c r="E42" s="11">
         <v>0</v>
       </c>
       <c r="F42" s="6">
-        <f t="shared" ref="F42:F44" si="14">F41-D42+E42</f>
-        <v>293586.99000000139</v>
+        <f t="shared" si="11"/>
+        <v>314192.64000000141</v>
       </c>
       <c r="G42" s="7"/>
       <c r="H42" s="8"/>
@@ -1548,17 +1551,17 @@
         <v>44958</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D43" s="11">
-        <v>0</v>
+        <v>47805.65</v>
       </c>
       <c r="E43" s="11">
-        <v>77827.240000000005</v>
+        <v>0</v>
       </c>
       <c r="F43" s="6">
-        <f t="shared" si="14"/>
-        <v>371414.23000000138</v>
+        <f t="shared" si="11"/>
+        <v>266386.99000000139</v>
       </c>
       <c r="G43" s="7"/>
       <c r="H43" s="8"/>
@@ -1570,66 +1573,66 @@
       <c r="B44" s="3">
         <v>44958</v>
       </c>
-      <c r="C44" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D44" s="9">
-        <v>14.98</v>
-      </c>
-      <c r="E44" s="9">
-        <v>0</v>
+      <c r="C44" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D44" s="11">
+        <v>0</v>
+      </c>
+      <c r="E44" s="11">
+        <v>77827.240000000005</v>
       </c>
       <c r="F44" s="6">
-        <f t="shared" si="14"/>
-        <v>371399.2500000014</v>
-      </c>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
+        <f t="shared" si="11"/>
+        <v>344214.23000000138</v>
+      </c>
+      <c r="G44" s="7"/>
+      <c r="H44" s="8"/>
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1">
       <c r="A45" s="3">
-        <v>44957</v>
+        <v>44956</v>
       </c>
       <c r="B45" s="3">
-        <v>44959</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D45" s="11">
-        <v>0</v>
-      </c>
-      <c r="E45" s="11">
-        <v>53630.95</v>
+        <v>44958</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" s="9">
+        <v>14.98</v>
+      </c>
+      <c r="E45" s="9">
+        <v>0</v>
       </c>
       <c r="F45" s="6">
-        <f t="shared" ref="F45" si="15">F44-D45+E45</f>
-        <v>425030.20000000141</v>
-      </c>
-      <c r="G45" s="7"/>
-      <c r="H45" s="8"/>
+        <f t="shared" si="11"/>
+        <v>344199.2500000014</v>
+      </c>
+      <c r="G45" s="10"/>
+      <c r="H45" s="10"/>
     </row>
     <row r="46" spans="1:8" ht="15" customHeight="1">
-      <c r="A46" s="3">
-        <v>44957</v>
+      <c r="A46" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="B46" s="3">
-        <v>44959</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D46" s="11">
-        <v>68551.5</v>
-      </c>
-      <c r="E46" s="11">
+        <v>44958</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="9">
+        <v>100</v>
+      </c>
+      <c r="E46" s="9">
         <v>0</v>
       </c>
       <c r="F46" s="6">
-        <f t="shared" ref="F46:F47" si="16">F45-D46+E46</f>
-        <v>356478.70000000141</v>
-      </c>
-      <c r="G46" s="7"/>
+        <f t="shared" si="11"/>
+        <v>344099.2500000014</v>
+      </c>
+      <c r="G46" s="10"/>
       <c r="H46" s="8"/>
     </row>
     <row r="47" spans="1:8" ht="15" customHeight="1">
@@ -1639,21 +1642,159 @@
       <c r="B47" s="3">
         <v>44959</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C47" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D47" s="11">
+        <v>0</v>
+      </c>
+      <c r="E47" s="11">
+        <v>53630.95</v>
+      </c>
+      <c r="F47" s="6">
+        <f t="shared" si="11"/>
+        <v>397730.20000000141</v>
+      </c>
+      <c r="G47" s="7"/>
+      <c r="H47" s="8"/>
+    </row>
+    <row r="48" spans="1:8" ht="15" customHeight="1">
+      <c r="A48" s="3">
+        <v>44957</v>
+      </c>
+      <c r="B48" s="3">
+        <v>44959</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" s="11">
+        <v>68551.5</v>
+      </c>
+      <c r="E48" s="11">
+        <v>0</v>
+      </c>
+      <c r="F48" s="6">
+        <f t="shared" si="11"/>
+        <v>329178.70000000141</v>
+      </c>
+      <c r="G48" s="7"/>
+      <c r="H48" s="8"/>
+    </row>
+    <row r="49" spans="1:8" ht="15" customHeight="1">
+      <c r="A49" s="3">
+        <v>44957</v>
+      </c>
+      <c r="B49" s="3">
+        <v>44959</v>
+      </c>
+      <c r="C49" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D47" s="9">
+      <c r="D49" s="9">
         <v>14.98</v>
       </c>
-      <c r="E47" s="9">
-        <v>0</v>
-      </c>
-      <c r="F47" s="6">
-        <f t="shared" si="16"/>
-        <v>356463.72000000143</v>
-      </c>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
+      <c r="E49" s="9">
+        <v>0</v>
+      </c>
+      <c r="F49" s="6">
+        <f t="shared" si="11"/>
+        <v>329163.72000000143</v>
+      </c>
+      <c r="G49" s="10"/>
+      <c r="H49" s="10"/>
+    </row>
+    <row r="50" spans="1:8" ht="15" customHeight="1">
+      <c r="A50" s="3">
+        <v>44958</v>
+      </c>
+      <c r="B50" s="3">
+        <v>44960</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D50" s="11">
+        <v>0</v>
+      </c>
+      <c r="E50" s="11">
+        <v>55875.97</v>
+      </c>
+      <c r="F50" s="6">
+        <f t="shared" si="11"/>
+        <v>385039.69000000146</v>
+      </c>
+      <c r="G50" s="7"/>
+      <c r="H50" s="8"/>
+    </row>
+    <row r="51" spans="1:8" ht="15" customHeight="1">
+      <c r="A51" s="3">
+        <v>44958</v>
+      </c>
+      <c r="B51" s="3">
+        <v>44960</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" s="9">
+        <v>14.98</v>
+      </c>
+      <c r="E51" s="9">
+        <v>0</v>
+      </c>
+      <c r="F51" s="6">
+        <f t="shared" si="11"/>
+        <v>385024.71000000148</v>
+      </c>
+      <c r="G51" s="10"/>
+      <c r="H51" s="10"/>
+    </row>
+    <row r="52" spans="1:8" ht="15" customHeight="1">
+      <c r="A52" s="3">
+        <v>44959</v>
+      </c>
+      <c r="B52" s="3">
+        <v>44963</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D52" s="11">
+        <v>90951</v>
+      </c>
+      <c r="E52" s="11">
+        <v>0</v>
+      </c>
+      <c r="F52" s="6">
+        <f t="shared" si="11"/>
+        <v>294073.71000000148</v>
+      </c>
+      <c r="G52" s="7"/>
+      <c r="H52" s="8"/>
+    </row>
+    <row r="53" spans="1:8" ht="15" customHeight="1">
+      <c r="A53" s="3">
+        <v>44959</v>
+      </c>
+      <c r="B53" s="3">
+        <v>44963</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="9">
+        <v>14.98</v>
+      </c>
+      <c r="E53" s="9">
+        <v>0</v>
+      </c>
+      <c r="F53" s="6">
+        <f t="shared" si="11"/>
+        <v>294058.73000000149</v>
+      </c>
+      <c r="G53" s="10"/>
+      <c r="H53" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6457" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0837A1ED-6713-4E6E-915A-18753C7CA42E}"/>
+  <xr:revisionPtr revIDLastSave="6464" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56FC58EF-2713-46D6-8136-B2E741F38BE7}"/>
   <bookViews>
     <workbookView xWindow="10368" yWindow="1740" windowWidth="13908" windowHeight="9516" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -566,7 +566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="11.42578125" style="2" customWidth="1"/>
@@ -1796,6 +1796,52 @@
       <c r="G53" s="10"/>
       <c r="H53" s="10"/>
     </row>
+    <row r="54" spans="1:8" ht="15" customHeight="1">
+      <c r="A54" s="3">
+        <v>44964</v>
+      </c>
+      <c r="B54" s="3">
+        <v>44966</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D54" s="11">
+        <v>183405.33</v>
+      </c>
+      <c r="E54" s="11">
+        <v>0</v>
+      </c>
+      <c r="F54" s="6">
+        <f t="shared" ref="F54:F55" si="12">F53-D54+E54</f>
+        <v>110653.40000000151</v>
+      </c>
+      <c r="G54" s="7"/>
+      <c r="H54" s="8"/>
+    </row>
+    <row r="55" spans="1:8" ht="15" customHeight="1">
+      <c r="A55" s="3">
+        <v>44964</v>
+      </c>
+      <c r="B55" s="3">
+        <v>44966</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D55" s="9">
+        <v>14.98</v>
+      </c>
+      <c r="E55" s="9">
+        <v>0</v>
+      </c>
+      <c r="F55" s="6">
+        <f t="shared" si="12"/>
+        <v>110638.42000000151</v>
+      </c>
+      <c r="G55" s="10"/>
+      <c r="H55" s="10"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26202"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6464" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56FC58EF-2713-46D6-8136-B2E741F38BE7}"/>
+  <xr:revisionPtr revIDLastSave="6476" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4551B4F-41C8-4579-88D1-5CD66CC58A5B}"/>
   <bookViews>
     <workbookView xWindow="10368" yWindow="1740" windowWidth="13908" windowHeight="9516" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="29">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -117,6 +117,9 @@
   </si>
   <si>
     <t>RCL</t>
+  </si>
+  <si>
+    <t>DCC</t>
   </si>
 </sst>
 </file>
@@ -566,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="11.42578125" style="2" customWidth="1"/>
@@ -1813,7 +1816,7 @@
         <v>0</v>
       </c>
       <c r="F54" s="6">
-        <f t="shared" ref="F54:F55" si="12">F53-D54+E54</f>
+        <f t="shared" ref="F54:F56" si="12">F53-D54+E54</f>
         <v>110653.40000000151</v>
       </c>
       <c r="G54" s="7"/>
@@ -1841,6 +1844,92 @@
       </c>
       <c r="G55" s="10"/>
       <c r="H55" s="10"/>
+    </row>
+    <row r="56" spans="1:8" ht="15" customHeight="1">
+      <c r="A56" s="3">
+        <v>44965</v>
+      </c>
+      <c r="B56" s="3">
+        <v>44967</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D56" s="11">
+        <v>0</v>
+      </c>
+      <c r="E56" s="11">
+        <v>54379.28</v>
+      </c>
+      <c r="F56" s="6">
+        <f t="shared" si="12"/>
+        <v>165017.70000000153</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="15" customHeight="1">
+      <c r="A57" s="3">
+        <v>44965</v>
+      </c>
+      <c r="B57" s="3">
+        <v>44967</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D57" s="11">
+        <v>0</v>
+      </c>
+      <c r="E57" s="11">
+        <v>54379.28</v>
+      </c>
+      <c r="F57" s="6">
+        <f t="shared" ref="F57" si="13">F56-D57+E57</f>
+        <v>219396.98000000152</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="15" customHeight="1">
+      <c r="A58" s="3">
+        <v>44965</v>
+      </c>
+      <c r="B58" s="3">
+        <v>44967</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D58" s="11">
+        <v>0</v>
+      </c>
+      <c r="E58" s="11">
+        <v>171219.93</v>
+      </c>
+      <c r="F58" s="6">
+        <f t="shared" ref="F58:F59" si="14">F57-D58+E58</f>
+        <v>390616.91000000155</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="15" customHeight="1">
+      <c r="A59" s="3">
+        <v>44965</v>
+      </c>
+      <c r="B59" s="3">
+        <v>44967</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" s="9">
+        <v>14.98</v>
+      </c>
+      <c r="E59" s="9">
+        <v>0</v>
+      </c>
+      <c r="F59" s="6">
+        <f t="shared" si="14"/>
+        <v>390601.93000000156</v>
+      </c>
+      <c r="G59" s="10"/>
+      <c r="H59" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6476" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4551B4F-41C8-4579-88D1-5CD66CC58A5B}"/>
+  <xr:revisionPtr revIDLastSave="6480" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86D8D34A-93A4-4B93-852D-1ADF079DA93E}"/>
   <bookViews>
     <workbookView xWindow="10368" yWindow="1740" windowWidth="13908" windowHeight="9516" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="29">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -569,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="11.42578125" style="2" customWidth="1"/>
@@ -1904,7 +1904,7 @@
         <v>171219.93</v>
       </c>
       <c r="F58" s="6">
-        <f t="shared" ref="F58:F59" si="14">F57-D58+E58</f>
+        <f t="shared" ref="F58" si="14">F57-D58+E58</f>
         <v>390616.91000000155</v>
       </c>
     </row>
@@ -1915,21 +1915,42 @@
       <c r="B59" s="3">
         <v>44967</v>
       </c>
-      <c r="C59" s="8" t="s">
+      <c r="C59" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D59" s="11">
+        <v>0</v>
+      </c>
+      <c r="E59" s="11">
+        <v>60116.55</v>
+      </c>
+      <c r="F59" s="6">
+        <f t="shared" ref="F59:F60" si="15">F58-D59+E59</f>
+        <v>450733.46000000153</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="15" customHeight="1">
+      <c r="A60" s="3">
+        <v>44965</v>
+      </c>
+      <c r="B60" s="3">
+        <v>44967</v>
+      </c>
+      <c r="C60" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D59" s="9">
+      <c r="D60" s="9">
         <v>14.98</v>
       </c>
-      <c r="E59" s="9">
-        <v>0</v>
-      </c>
-      <c r="F59" s="6">
-        <f t="shared" si="14"/>
-        <v>390601.93000000156</v>
-      </c>
-      <c r="G59" s="10"/>
-      <c r="H59" s="10"/>
+      <c r="E60" s="9">
+        <v>0</v>
+      </c>
+      <c r="F60" s="6">
+        <f t="shared" si="15"/>
+        <v>450718.48000000155</v>
+      </c>
+      <c r="G60" s="10"/>
+      <c r="H60" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26202"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26207"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6480" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86D8D34A-93A4-4B93-852D-1ADF079DA93E}"/>
+  <xr:revisionPtr revIDLastSave="6491" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{962B38D3-1C16-4C1E-B29A-8AAFAA7CA467}"/>
   <bookViews>
     <workbookView xWindow="10368" yWindow="1740" windowWidth="13908" windowHeight="9516" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="29">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -213,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -221,10 +221,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="189" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="188" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="189" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -569,87 +567,81 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="11.42578125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" style="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.7109375" style="5" customWidth="1"/>
     <col min="5" max="5" width="14.28515625" style="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8" style="2" customWidth="1"/>
-    <col min="9" max="13" width="10.140625" style="2"/>
-    <col min="14" max="14" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="10.140625" style="2"/>
+    <col min="7" max="11" width="10.140625" style="2"/>
+    <col min="12" max="12" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="10.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" customHeight="1">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13" t="s">
+    <row r="1" spans="1:6" ht="15" customHeight="1">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1">
+    <row r="2" spans="1:6" ht="15" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="3">
         <v>44927</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="8">
         <v>1310</v>
       </c>
-      <c r="E2" s="9">
-        <v>0</v>
-      </c>
-      <c r="F2" s="16">
+      <c r="E2" s="8">
+        <v>0</v>
+      </c>
+      <c r="F2" s="14">
         <v>214038.73000000126</v>
       </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="8"/>
-    </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="3">
         <v>44930</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="8">
         <v>1900</v>
       </c>
-      <c r="E3" s="9">
-        <v>0</v>
-      </c>
-      <c r="F3" s="16">
+      <c r="E3" s="8">
+        <v>0</v>
+      </c>
+      <c r="F3" s="14">
         <f t="shared" ref="F3" si="0">F2-D3+E3</f>
         <v>212138.73000000126</v>
       </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-    </row>
-    <row r="4" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="4" spans="1:6" ht="15" customHeight="1">
       <c r="A4" s="3">
         <v>44925</v>
       </c>
@@ -659,43 +651,39 @@
       <c r="C4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="11">
-        <v>0</v>
-      </c>
-      <c r="E4" s="11">
+      <c r="D4" s="9">
+        <v>0</v>
+      </c>
+      <c r="E4" s="9">
         <v>49390.36</v>
       </c>
       <c r="F4" s="6">
         <f>F3-D4+E4</f>
         <v>261529.09000000125</v>
       </c>
-      <c r="G4" s="7"/>
-      <c r="H4" s="8"/>
-    </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="5" spans="1:6" ht="15" customHeight="1">
       <c r="A5" s="3">
         <v>44925</v>
       </c>
       <c r="B5" s="3">
         <v>44930</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="8">
         <v>14.98</v>
       </c>
-      <c r="E5" s="9">
-        <v>0</v>
-      </c>
-      <c r="F5" s="16">
+      <c r="E5" s="8">
+        <v>0</v>
+      </c>
+      <c r="F5" s="14">
         <f t="shared" ref="F5" si="1">F4-D5+E5</f>
         <v>261514.11000000124</v>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-    </row>
-    <row r="6" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="6" spans="1:6" ht="15" customHeight="1">
       <c r="A6" s="3">
         <v>44929</v>
       </c>
@@ -705,43 +693,39 @@
       <c r="C6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="11">
-        <v>0</v>
-      </c>
-      <c r="E6" s="11">
+      <c r="D6" s="9">
+        <v>0</v>
+      </c>
+      <c r="E6" s="9">
         <v>98032.38</v>
       </c>
       <c r="F6" s="6">
         <f t="shared" ref="F6:F7" si="2">F5-D6+E6</f>
         <v>359546.49000000127</v>
       </c>
-      <c r="G6" s="7"/>
-      <c r="H6" s="8"/>
-    </row>
-    <row r="7" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="7" spans="1:6" ht="15" customHeight="1">
       <c r="A7" s="3">
         <v>44929</v>
       </c>
       <c r="B7" s="3">
         <v>44931</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="8">
         <v>14.98</v>
       </c>
-      <c r="E7" s="9">
-        <v>0</v>
-      </c>
-      <c r="F7" s="16">
+      <c r="E7" s="8">
+        <v>0</v>
+      </c>
+      <c r="F7" s="14">
         <f t="shared" si="2"/>
         <v>359531.51000000129</v>
       </c>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-    </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="8" spans="1:6" ht="15" customHeight="1">
       <c r="A8" s="3">
         <v>44930</v>
       </c>
@@ -751,43 +735,39 @@
       <c r="C8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="9">
         <v>99219.28</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="9">
         <v>0</v>
       </c>
       <c r="F8" s="6">
         <f t="shared" ref="F8:F9" si="3">F7-D8+E8</f>
         <v>260312.23000000129</v>
       </c>
-      <c r="G8" s="7"/>
-      <c r="H8" s="8"/>
-    </row>
-    <row r="9" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="9" spans="1:6" ht="15" customHeight="1">
       <c r="A9" s="3">
         <v>44930</v>
       </c>
       <c r="B9" s="3">
         <v>44932</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="8">
         <v>14.98</v>
       </c>
-      <c r="E9" s="9">
-        <v>0</v>
-      </c>
-      <c r="F9" s="16">
+      <c r="E9" s="8">
+        <v>0</v>
+      </c>
+      <c r="F9" s="14">
         <f t="shared" si="3"/>
         <v>260297.25000000128</v>
       </c>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-    </row>
-    <row r="10" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="10" spans="1:6" ht="15" customHeight="1">
       <c r="A10" s="3">
         <v>44932</v>
       </c>
@@ -797,43 +777,39 @@
       <c r="C10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="9">
         <v>147926.92000000001</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="9">
         <v>0</v>
       </c>
       <c r="F10" s="6">
         <f t="shared" ref="F10:F12" si="4">F9-D10+E10</f>
         <v>112370.33000000127</v>
       </c>
-      <c r="G10" s="7"/>
-      <c r="H10" s="8"/>
-    </row>
-    <row r="11" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="11" spans="1:6" ht="15" customHeight="1">
       <c r="A11" s="3">
         <v>44932</v>
       </c>
       <c r="B11" s="3">
         <v>44936</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="8">
         <v>14.98</v>
       </c>
-      <c r="E11" s="9">
-        <v>0</v>
-      </c>
-      <c r="F11" s="16">
+      <c r="E11" s="8">
+        <v>0</v>
+      </c>
+      <c r="F11" s="14">
         <f t="shared" si="4"/>
         <v>112355.35000000127</v>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-    </row>
-    <row r="12" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="12" spans="1:6" ht="15" customHeight="1">
       <c r="A12" s="3">
         <v>44935</v>
       </c>
@@ -843,20 +819,18 @@
       <c r="C12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="11">
-        <v>0</v>
-      </c>
-      <c r="E12" s="11">
+      <c r="D12" s="9">
+        <v>0</v>
+      </c>
+      <c r="E12" s="9">
         <v>125720.92</v>
       </c>
       <c r="F12" s="6">
         <f t="shared" si="4"/>
         <v>238076.27000000127</v>
       </c>
-      <c r="G12" s="7"/>
-      <c r="H12" s="8"/>
-    </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="13" spans="1:6" ht="15" customHeight="1">
       <c r="A13" s="3">
         <v>44935</v>
       </c>
@@ -866,135 +840,123 @@
       <c r="C13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="11">
-        <v>0</v>
-      </c>
-      <c r="E13" s="11">
+      <c r="D13" s="9">
+        <v>0</v>
+      </c>
+      <c r="E13" s="9">
         <v>105066.77</v>
       </c>
       <c r="F13" s="6">
         <f t="shared" ref="F13:F14" si="5">F12-D13+E13</f>
         <v>343143.04000000126</v>
       </c>
-      <c r="G13" s="7"/>
-      <c r="H13" s="8"/>
-    </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="14" spans="1:6" ht="15" customHeight="1">
       <c r="A14" s="3">
         <v>44935</v>
       </c>
       <c r="B14" s="3">
         <v>44937</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="8">
         <v>14.98</v>
       </c>
-      <c r="E14" s="9">
-        <v>0</v>
-      </c>
-      <c r="F14" s="16">
+      <c r="E14" s="8">
+        <v>0</v>
+      </c>
+      <c r="F14" s="14">
         <f t="shared" si="5"/>
         <v>343128.06000000128</v>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-    </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="15" spans="1:6" ht="15" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B15" s="3">
         <v>44940</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="8">
         <v>20</v>
       </c>
-      <c r="E15" s="9">
-        <v>0</v>
-      </c>
-      <c r="F15" s="16">
+      <c r="E15" s="8">
+        <v>0</v>
+      </c>
+      <c r="F15" s="14">
         <f t="shared" ref="F15" si="6">F14-D15+E15</f>
         <v>343108.06000000128</v>
       </c>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-    </row>
-    <row r="16" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="16" spans="1:6" ht="15" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="3">
         <v>44941</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="8">
         <v>225</v>
       </c>
-      <c r="E16" s="9">
-        <v>0</v>
-      </c>
-      <c r="F16" s="16">
+      <c r="E16" s="8">
+        <v>0</v>
+      </c>
+      <c r="F16" s="14">
         <f>F15-D16+E16</f>
         <v>342883.06000000128</v>
       </c>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-    </row>
-    <row r="17" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="17" spans="1:6" ht="15" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="3">
         <v>44942</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="8">
         <v>240</v>
       </c>
-      <c r="E17" s="9">
-        <v>0</v>
-      </c>
-      <c r="F17" s="16">
+      <c r="E17" s="8">
+        <v>0</v>
+      </c>
+      <c r="F17" s="14">
         <f>F16-D17+E17</f>
         <v>342643.06000000128</v>
       </c>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-    </row>
-    <row r="18" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="18" spans="1:6" ht="15" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B18" s="3">
         <v>44945</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="9">
-        <v>0</v>
-      </c>
-      <c r="E18" s="9">
+      <c r="D18" s="8">
+        <v>0</v>
+      </c>
+      <c r="E18" s="8">
         <v>304081.40000000002</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="14">
         <f t="shared" ref="F18:F26" si="7">F17-D18+E18</f>
         <v>646724.46000000136</v>
       </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-    </row>
-    <row r="19" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="19" spans="1:6" ht="15" customHeight="1">
       <c r="A19" s="3">
         <v>44943</v>
       </c>
@@ -1004,20 +966,18 @@
       <c r="C19" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="11">
-        <v>0</v>
-      </c>
-      <c r="E19" s="11">
+      <c r="D19" s="9">
+        <v>0</v>
+      </c>
+      <c r="E19" s="9">
         <v>151912.78</v>
       </c>
       <c r="F19" s="6">
         <f t="shared" si="7"/>
         <v>798637.24000000139</v>
       </c>
-      <c r="G19" s="7"/>
-      <c r="H19" s="8"/>
-    </row>
-    <row r="20" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="20" spans="1:6" ht="15" customHeight="1">
       <c r="A20" s="3">
         <v>44943</v>
       </c>
@@ -1027,43 +987,39 @@
       <c r="C20" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="9">
         <v>89197.13</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="9">
         <v>0</v>
       </c>
       <c r="F20" s="6">
         <f t="shared" si="7"/>
         <v>709440.11000000138</v>
       </c>
-      <c r="G20" s="7"/>
-      <c r="H20" s="8"/>
-    </row>
-    <row r="21" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="21" spans="1:6" ht="15" customHeight="1">
       <c r="A21" s="3">
         <v>44943</v>
       </c>
       <c r="B21" s="3">
         <v>44945</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="8">
         <v>14.98</v>
       </c>
-      <c r="E21" s="9">
-        <v>0</v>
-      </c>
-      <c r="F21" s="16">
+      <c r="E21" s="8">
+        <v>0</v>
+      </c>
+      <c r="F21" s="14">
         <f t="shared" si="7"/>
         <v>709425.1300000014</v>
       </c>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-    </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="22" spans="1:6" ht="15" customHeight="1">
       <c r="A22" s="3">
         <v>44944</v>
       </c>
@@ -1073,43 +1029,39 @@
       <c r="C22" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="9">
         <v>89197.13</v>
       </c>
-      <c r="E22" s="11">
+      <c r="E22" s="9">
         <v>0</v>
       </c>
       <c r="F22" s="6">
         <f t="shared" si="7"/>
         <v>620228.0000000014</v>
       </c>
-      <c r="G22" s="7"/>
-      <c r="H22" s="8"/>
-    </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="23" spans="1:6" ht="15" customHeight="1">
       <c r="A23" s="3">
         <v>44944</v>
       </c>
       <c r="B23" s="3">
         <v>44946</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="8">
         <v>14.98</v>
       </c>
-      <c r="E23" s="9">
-        <v>0</v>
-      </c>
-      <c r="F23" s="16">
+      <c r="E23" s="8">
+        <v>0</v>
+      </c>
+      <c r="F23" s="14">
         <f t="shared" si="7"/>
         <v>620213.02000000142</v>
       </c>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-    </row>
-    <row r="24" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="24" spans="1:6" ht="15" customHeight="1">
       <c r="A24" s="3">
         <v>44945</v>
       </c>
@@ -1119,20 +1071,18 @@
       <c r="C24" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="9">
         <v>101023.27</v>
       </c>
-      <c r="E24" s="11">
+      <c r="E24" s="9">
         <v>0</v>
       </c>
       <c r="F24" s="6">
         <f t="shared" si="7"/>
         <v>519189.7500000014</v>
       </c>
-      <c r="G24" s="7"/>
-      <c r="H24" s="8"/>
-    </row>
-    <row r="25" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="25" spans="1:6" ht="15" customHeight="1">
       <c r="A25" s="3">
         <v>44945</v>
       </c>
@@ -1142,43 +1092,39 @@
       <c r="C25" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D25" s="11">
-        <v>0</v>
-      </c>
-      <c r="E25" s="11">
+      <c r="D25" s="9">
+        <v>0</v>
+      </c>
+      <c r="E25" s="9">
         <v>52882.61</v>
       </c>
       <c r="F25" s="6">
         <f t="shared" si="7"/>
         <v>572072.36000000138</v>
       </c>
-      <c r="G25" s="7"/>
-      <c r="H25" s="8"/>
-    </row>
-    <row r="26" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="26" spans="1:6" ht="15" customHeight="1">
       <c r="A26" s="3">
         <v>44945</v>
       </c>
       <c r="B26" s="3">
         <v>45100</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="8">
         <v>14.98</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E26" s="8">
         <v>0</v>
       </c>
       <c r="F26" s="6">
         <f t="shared" si="7"/>
         <v>572057.3800000014</v>
       </c>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-    </row>
-    <row r="27" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="27" spans="1:6" ht="15" customHeight="1">
       <c r="A27" s="3">
         <v>44946</v>
       </c>
@@ -1188,89 +1134,81 @@
       <c r="C27" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="11">
+      <c r="D27" s="9">
         <v>142514.95000000001</v>
       </c>
-      <c r="E27" s="11">
+      <c r="E27" s="9">
         <v>0</v>
       </c>
       <c r="F27" s="6">
         <f t="shared" ref="F27:F29" si="8">F26-D27+E27</f>
         <v>429542.43000000139</v>
       </c>
-      <c r="G27" s="7"/>
-      <c r="H27" s="8"/>
-    </row>
-    <row r="28" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="28" spans="1:6" ht="15" customHeight="1">
       <c r="A28" s="3">
         <v>44946</v>
       </c>
       <c r="B28" s="3">
         <v>44950</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="8">
         <v>14.98</v>
       </c>
-      <c r="E28" s="9">
+      <c r="E28" s="8">
         <v>0</v>
       </c>
       <c r="F28" s="6">
         <f t="shared" si="8"/>
         <v>429527.45000000141</v>
       </c>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-    </row>
-    <row r="29" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="29" spans="1:6" ht="15" customHeight="1">
       <c r="A29" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B29" s="3">
         <v>44950</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="8">
         <v>29500</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="8">
         <v>0</v>
       </c>
       <c r="F29" s="6">
         <f t="shared" si="8"/>
         <v>400027.45000000141</v>
       </c>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-    </row>
-    <row r="30" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="30" spans="1:6" ht="15" customHeight="1">
       <c r="A30" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B30" s="3">
         <v>44951</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D30" s="9">
-        <v>0</v>
-      </c>
-      <c r="E30" s="9">
+      <c r="D30" s="8">
+        <v>0</v>
+      </c>
+      <c r="E30" s="8">
         <v>102052.5</v>
       </c>
       <c r="F30" s="6">
         <f t="shared" ref="F30:F36" si="9">F29-D30+E30</f>
         <v>502079.95000000141</v>
       </c>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-    </row>
-    <row r="31" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="31" spans="1:6" ht="15" customHeight="1">
       <c r="A31" s="3">
         <v>44950</v>
       </c>
@@ -1280,20 +1218,18 @@
       <c r="C31" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D31" s="11">
-        <v>0</v>
-      </c>
-      <c r="E31" s="11">
+      <c r="D31" s="9">
+        <v>0</v>
+      </c>
+      <c r="E31" s="9">
         <v>318044</v>
       </c>
       <c r="F31" s="6">
         <f t="shared" si="9"/>
         <v>820123.95000000135</v>
       </c>
-      <c r="G31" s="7"/>
-      <c r="H31" s="8"/>
-    </row>
-    <row r="32" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="32" spans="1:6" ht="15" customHeight="1">
       <c r="A32" s="3">
         <v>44950</v>
       </c>
@@ -1303,43 +1239,39 @@
       <c r="C32" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D32" s="11">
+      <c r="D32" s="9">
         <v>195431.91</v>
       </c>
-      <c r="E32" s="11">
+      <c r="E32" s="9">
         <v>0</v>
       </c>
       <c r="F32" s="6">
         <f t="shared" si="9"/>
         <v>624692.04000000132</v>
       </c>
-      <c r="G32" s="7"/>
-      <c r="H32" s="8"/>
-    </row>
-    <row r="33" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="33" spans="1:6" ht="15" customHeight="1">
       <c r="A33" s="3">
         <v>44950</v>
       </c>
       <c r="B33" s="3">
         <v>44952</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D33" s="9">
+      <c r="D33" s="8">
         <v>14.98</v>
       </c>
-      <c r="E33" s="9">
+      <c r="E33" s="8">
         <v>0</v>
       </c>
       <c r="F33" s="6">
         <f t="shared" si="9"/>
         <v>624677.06000000134</v>
       </c>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-    </row>
-    <row r="34" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="34" spans="1:6" ht="15" customHeight="1">
       <c r="A34" s="3">
         <v>44951</v>
       </c>
@@ -1349,20 +1281,18 @@
       <c r="C34" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D34" s="11">
-        <v>0</v>
-      </c>
-      <c r="E34" s="11">
+      <c r="D34" s="9">
+        <v>0</v>
+      </c>
+      <c r="E34" s="9">
         <v>53381.5</v>
       </c>
       <c r="F34" s="6">
         <f t="shared" si="9"/>
         <v>678058.56000000134</v>
       </c>
-      <c r="G34" s="7"/>
-      <c r="H34" s="8"/>
-    </row>
-    <row r="35" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="35" spans="1:6" ht="15" customHeight="1">
       <c r="A35" s="3">
         <v>44951</v>
       </c>
@@ -1372,43 +1302,39 @@
       <c r="C35" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D35" s="11">
-        <v>0</v>
-      </c>
-      <c r="E35" s="11">
+      <c r="D35" s="9">
+        <v>0</v>
+      </c>
+      <c r="E35" s="9">
         <v>54628.74</v>
       </c>
       <c r="F35" s="6">
         <f t="shared" si="9"/>
         <v>732687.30000000133</v>
       </c>
-      <c r="G35" s="7"/>
-      <c r="H35" s="8"/>
-    </row>
-    <row r="36" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="36" spans="1:6" ht="15" customHeight="1">
       <c r="A36" s="3">
         <v>44951</v>
       </c>
       <c r="B36" s="3">
         <v>44953</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D36" s="8">
         <v>14.98</v>
       </c>
-      <c r="E36" s="9">
-        <v>0</v>
-      </c>
-      <c r="F36" s="16">
+      <c r="E36" s="8">
+        <v>0</v>
+      </c>
+      <c r="F36" s="14">
         <f t="shared" si="9"/>
         <v>732672.32000000135</v>
       </c>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-    </row>
-    <row r="37" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="37" spans="1:6" ht="15" customHeight="1">
       <c r="A37" s="3">
         <v>44952</v>
       </c>
@@ -1418,20 +1344,18 @@
       <c r="C37" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D37" s="11">
+      <c r="D37" s="9">
         <v>140710.97</v>
       </c>
-      <c r="E37" s="11">
+      <c r="E37" s="9">
         <v>0</v>
       </c>
       <c r="F37" s="6">
         <f t="shared" ref="F37" si="10">F36-D37+E37</f>
         <v>591961.35000000137</v>
       </c>
-      <c r="G37" s="7"/>
-      <c r="H37" s="8"/>
-    </row>
-    <row r="38" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="38" spans="1:6" ht="15" customHeight="1">
       <c r="A38" s="3">
         <v>44952</v>
       </c>
@@ -1441,66 +1365,60 @@
       <c r="C38" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D38" s="11">
+      <c r="D38" s="9">
         <v>96212.63</v>
       </c>
-      <c r="E38" s="11">
+      <c r="E38" s="9">
         <v>0</v>
       </c>
       <c r="F38" s="6">
         <f t="shared" ref="F38:F53" si="11">F37-D38+E38</f>
         <v>495748.72000000137</v>
       </c>
-      <c r="G38" s="7"/>
-      <c r="H38" s="8"/>
-    </row>
-    <row r="39" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="39" spans="1:6" ht="15" customHeight="1">
       <c r="A39" s="3">
         <v>44952</v>
       </c>
       <c r="B39" s="3">
         <v>44956</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D39" s="9">
+      <c r="D39" s="8">
         <v>14.98</v>
       </c>
-      <c r="E39" s="9">
+      <c r="E39" s="8">
         <v>0</v>
       </c>
       <c r="F39" s="6">
         <f t="shared" si="11"/>
         <v>495733.74000000139</v>
       </c>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-    </row>
-    <row r="40" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="40" spans="1:6" ht="15" customHeight="1">
       <c r="A40" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B40" s="3">
         <v>44957</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D40" s="9">
+      <c r="D40" s="8">
         <v>27200</v>
       </c>
-      <c r="E40" s="9">
+      <c r="E40" s="8">
         <v>0</v>
       </c>
       <c r="F40" s="6">
         <f t="shared" si="11"/>
         <v>468533.74000000139</v>
       </c>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-    </row>
-    <row r="41" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="41" spans="1:6" ht="15" customHeight="1">
       <c r="A41" s="3">
         <v>44956</v>
       </c>
@@ -1510,20 +1428,18 @@
       <c r="C41" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D41" s="11">
+      <c r="D41" s="9">
         <v>77170.55</v>
       </c>
-      <c r="E41" s="11">
+      <c r="E41" s="9">
         <v>0</v>
       </c>
       <c r="F41" s="6">
         <f t="shared" si="11"/>
         <v>391363.1900000014</v>
       </c>
-      <c r="G41" s="7"/>
-      <c r="H41" s="8"/>
-    </row>
-    <row r="42" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="42" spans="1:6" ht="15" customHeight="1">
       <c r="A42" s="3">
         <v>44956</v>
       </c>
@@ -1533,20 +1449,18 @@
       <c r="C42" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D42" s="11">
+      <c r="D42" s="9">
         <v>77170.55</v>
       </c>
-      <c r="E42" s="11">
+      <c r="E42" s="9">
         <v>0</v>
       </c>
       <c r="F42" s="6">
         <f t="shared" si="11"/>
         <v>314192.64000000141</v>
       </c>
-      <c r="G42" s="7"/>
-      <c r="H42" s="8"/>
-    </row>
-    <row r="43" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="43" spans="1:6" ht="15" customHeight="1">
       <c r="A43" s="3">
         <v>44956</v>
       </c>
@@ -1556,20 +1470,18 @@
       <c r="C43" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D43" s="11">
+      <c r="D43" s="9">
         <v>47805.65</v>
       </c>
-      <c r="E43" s="11">
+      <c r="E43" s="9">
         <v>0</v>
       </c>
       <c r="F43" s="6">
         <f t="shared" si="11"/>
         <v>266386.99000000139</v>
       </c>
-      <c r="G43" s="7"/>
-      <c r="H43" s="8"/>
-    </row>
-    <row r="44" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="44" spans="1:6" ht="15" customHeight="1">
       <c r="A44" s="3">
         <v>44956</v>
       </c>
@@ -1579,66 +1491,60 @@
       <c r="C44" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D44" s="11">
-        <v>0</v>
-      </c>
-      <c r="E44" s="11">
+      <c r="D44" s="9">
+        <v>0</v>
+      </c>
+      <c r="E44" s="9">
         <v>77827.240000000005</v>
       </c>
       <c r="F44" s="6">
         <f t="shared" si="11"/>
         <v>344214.23000000138</v>
       </c>
-      <c r="G44" s="7"/>
-      <c r="H44" s="8"/>
-    </row>
-    <row r="45" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="45" spans="1:6" ht="15" customHeight="1">
       <c r="A45" s="3">
         <v>44956</v>
       </c>
       <c r="B45" s="3">
         <v>44958</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D45" s="9">
+      <c r="D45" s="8">
         <v>14.98</v>
       </c>
-      <c r="E45" s="9">
+      <c r="E45" s="8">
         <v>0</v>
       </c>
       <c r="F45" s="6">
         <f t="shared" si="11"/>
         <v>344199.2500000014</v>
       </c>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-    </row>
-    <row r="46" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="46" spans="1:6" ht="15" customHeight="1">
       <c r="A46" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B46" s="3">
         <v>44958</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C46" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D46" s="9">
-        <v>100</v>
-      </c>
-      <c r="E46" s="9">
-        <v>0</v>
-      </c>
-      <c r="F46" s="6">
+      <c r="D46" s="8">
+        <v>1200</v>
+      </c>
+      <c r="E46" s="8">
+        <v>0</v>
+      </c>
+      <c r="F46" s="14">
         <f t="shared" si="11"/>
-        <v>344099.2500000014</v>
-      </c>
-      <c r="G46" s="10"/>
-      <c r="H46" s="8"/>
-    </row>
-    <row r="47" spans="1:8" ht="15" customHeight="1">
+        <v>342999.2500000014</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15" customHeight="1">
       <c r="A47" s="3">
         <v>44957</v>
       </c>
@@ -1648,20 +1554,18 @@
       <c r="C47" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D47" s="11">
-        <v>0</v>
-      </c>
-      <c r="E47" s="11">
+      <c r="D47" s="9">
+        <v>0</v>
+      </c>
+      <c r="E47" s="9">
         <v>53630.95</v>
       </c>
       <c r="F47" s="6">
         <f t="shared" si="11"/>
-        <v>397730.20000000141</v>
-      </c>
-      <c r="G47" s="7"/>
-      <c r="H47" s="8"/>
-    </row>
-    <row r="48" spans="1:8" ht="15" customHeight="1">
+        <v>396630.20000000141</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15" customHeight="1">
       <c r="A48" s="3">
         <v>44957</v>
       </c>
@@ -1671,43 +1575,39 @@
       <c r="C48" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D48" s="11">
+      <c r="D48" s="9">
         <v>68551.5</v>
       </c>
-      <c r="E48" s="11">
+      <c r="E48" s="9">
         <v>0</v>
       </c>
       <c r="F48" s="6">
         <f t="shared" si="11"/>
-        <v>329178.70000000141</v>
-      </c>
-      <c r="G48" s="7"/>
-      <c r="H48" s="8"/>
-    </row>
-    <row r="49" spans="1:8" ht="15" customHeight="1">
+        <v>328078.70000000141</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15" customHeight="1">
       <c r="A49" s="3">
         <v>44957</v>
       </c>
       <c r="B49" s="3">
         <v>44959</v>
       </c>
-      <c r="C49" s="8" t="s">
+      <c r="C49" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D49" s="9">
+      <c r="D49" s="8">
         <v>14.98</v>
       </c>
-      <c r="E49" s="9">
+      <c r="E49" s="8">
         <v>0</v>
       </c>
       <c r="F49" s="6">
         <f t="shared" si="11"/>
-        <v>329163.72000000143</v>
-      </c>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
-    </row>
-    <row r="50" spans="1:8" ht="15" customHeight="1">
+        <v>328063.72000000143</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15" customHeight="1">
       <c r="A50" s="3">
         <v>44958</v>
       </c>
@@ -1717,43 +1617,39 @@
       <c r="C50" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D50" s="11">
-        <v>0</v>
-      </c>
-      <c r="E50" s="11">
+      <c r="D50" s="9">
+        <v>0</v>
+      </c>
+      <c r="E50" s="9">
         <v>55875.97</v>
       </c>
       <c r="F50" s="6">
         <f t="shared" si="11"/>
-        <v>385039.69000000146</v>
-      </c>
-      <c r="G50" s="7"/>
-      <c r="H50" s="8"/>
-    </row>
-    <row r="51" spans="1:8" ht="15" customHeight="1">
+        <v>383939.69000000146</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15" customHeight="1">
       <c r="A51" s="3">
         <v>44958</v>
       </c>
       <c r="B51" s="3">
         <v>44960</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="C51" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D51" s="9">
+      <c r="D51" s="8">
         <v>14.98</v>
       </c>
-      <c r="E51" s="9">
+      <c r="E51" s="8">
         <v>0</v>
       </c>
       <c r="F51" s="6">
         <f t="shared" si="11"/>
-        <v>385024.71000000148</v>
-      </c>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-    </row>
-    <row r="52" spans="1:8" ht="15" customHeight="1">
+        <v>383924.71000000148</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15" customHeight="1">
       <c r="A52" s="3">
         <v>44959</v>
       </c>
@@ -1763,43 +1659,39 @@
       <c r="C52" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D52" s="11">
+      <c r="D52" s="9">
         <v>90951</v>
       </c>
-      <c r="E52" s="11">
+      <c r="E52" s="9">
         <v>0</v>
       </c>
       <c r="F52" s="6">
         <f t="shared" si="11"/>
-        <v>294073.71000000148</v>
-      </c>
-      <c r="G52" s="7"/>
-      <c r="H52" s="8"/>
-    </row>
-    <row r="53" spans="1:8" ht="15" customHeight="1">
+        <v>292973.71000000148</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="15" customHeight="1">
       <c r="A53" s="3">
         <v>44959</v>
       </c>
       <c r="B53" s="3">
         <v>44963</v>
       </c>
-      <c r="C53" s="8" t="s">
+      <c r="C53" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D53" s="9">
+      <c r="D53" s="8">
         <v>14.98</v>
       </c>
-      <c r="E53" s="9">
+      <c r="E53" s="8">
         <v>0</v>
       </c>
       <c r="F53" s="6">
         <f t="shared" si="11"/>
-        <v>294058.73000000149</v>
-      </c>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
-    </row>
-    <row r="54" spans="1:8" ht="15" customHeight="1">
+        <v>292958.73000000149</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="15" customHeight="1">
       <c r="A54" s="3">
         <v>44964</v>
       </c>
@@ -1809,43 +1701,39 @@
       <c r="C54" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D54" s="11">
+      <c r="D54" s="9">
         <v>183405.33</v>
       </c>
-      <c r="E54" s="11">
+      <c r="E54" s="9">
         <v>0</v>
       </c>
       <c r="F54" s="6">
         <f t="shared" ref="F54:F56" si="12">F53-D54+E54</f>
-        <v>110653.40000000151</v>
-      </c>
-      <c r="G54" s="7"/>
-      <c r="H54" s="8"/>
-    </row>
-    <row r="55" spans="1:8" ht="15" customHeight="1">
+        <v>109553.40000000151</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="15" customHeight="1">
       <c r="A55" s="3">
         <v>44964</v>
       </c>
       <c r="B55" s="3">
         <v>44966</v>
       </c>
-      <c r="C55" s="8" t="s">
+      <c r="C55" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D55" s="9">
+      <c r="D55" s="8">
         <v>14.98</v>
       </c>
-      <c r="E55" s="9">
+      <c r="E55" s="8">
         <v>0</v>
       </c>
       <c r="F55" s="6">
         <f t="shared" si="12"/>
-        <v>110638.42000000151</v>
-      </c>
-      <c r="G55" s="10"/>
-      <c r="H55" s="10"/>
-    </row>
-    <row r="56" spans="1:8" ht="15" customHeight="1">
+        <v>109538.42000000151</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="15" customHeight="1">
       <c r="A56" s="3">
         <v>44965</v>
       </c>
@@ -1855,18 +1743,18 @@
       <c r="C56" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D56" s="11">
-        <v>0</v>
-      </c>
-      <c r="E56" s="11">
+      <c r="D56" s="9">
+        <v>0</v>
+      </c>
+      <c r="E56" s="9">
         <v>54379.28</v>
       </c>
       <c r="F56" s="6">
         <f t="shared" si="12"/>
-        <v>165017.70000000153</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="15" customHeight="1">
+        <v>163917.70000000153</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15" customHeight="1">
       <c r="A57" s="3">
         <v>44965</v>
       </c>
@@ -1876,18 +1764,18 @@
       <c r="C57" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D57" s="11">
-        <v>0</v>
-      </c>
-      <c r="E57" s="11">
+      <c r="D57" s="9">
+        <v>0</v>
+      </c>
+      <c r="E57" s="9">
         <v>54379.28</v>
       </c>
       <c r="F57" s="6">
         <f t="shared" ref="F57" si="13">F56-D57+E57</f>
-        <v>219396.98000000152</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="15" customHeight="1">
+        <v>218296.98000000152</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="15" customHeight="1">
       <c r="A58" s="3">
         <v>44965</v>
       </c>
@@ -1897,18 +1785,18 @@
       <c r="C58" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D58" s="11">
-        <v>0</v>
-      </c>
-      <c r="E58" s="11">
+      <c r="D58" s="9">
+        <v>0</v>
+      </c>
+      <c r="E58" s="9">
         <v>171219.93</v>
       </c>
       <c r="F58" s="6">
         <f t="shared" ref="F58" si="14">F57-D58+E58</f>
-        <v>390616.91000000155</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" ht="15" customHeight="1">
+        <v>389516.91000000155</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="15" customHeight="1">
       <c r="A59" s="3">
         <v>44965</v>
       </c>
@@ -1918,39 +1806,58 @@
       <c r="C59" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D59" s="11">
-        <v>0</v>
-      </c>
-      <c r="E59" s="11">
+      <c r="D59" s="9">
+        <v>0</v>
+      </c>
+      <c r="E59" s="9">
         <v>60116.55</v>
       </c>
       <c r="F59" s="6">
-        <f t="shared" ref="F59:F60" si="15">F58-D59+E59</f>
-        <v>450733.46000000153</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" ht="15" customHeight="1">
+        <f t="shared" ref="F59:F61" si="15">F58-D59+E59</f>
+        <v>449633.46000000153</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="15" customHeight="1">
       <c r="A60" s="3">
         <v>44965</v>
       </c>
       <c r="B60" s="3">
         <v>44967</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="C60" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D60" s="9">
+      <c r="D60" s="8">
         <v>14.98</v>
       </c>
-      <c r="E60" s="9">
+      <c r="E60" s="8">
         <v>0</v>
       </c>
       <c r="F60" s="6">
         <f t="shared" si="15"/>
-        <v>450718.48000000155</v>
-      </c>
-      <c r="G60" s="10"/>
-      <c r="H60" s="10"/>
+        <v>449618.48000000155</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="15" customHeight="1">
+      <c r="A61" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B61" s="3">
+        <v>44967</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="8">
+        <v>50000</v>
+      </c>
+      <c r="E61" s="8">
+        <v>0</v>
+      </c>
+      <c r="F61" s="14">
+        <f t="shared" si="15"/>
+        <v>399618.48000000155</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26212"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6491" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{962B38D3-1C16-4C1E-B29A-8AAFAA7CA467}"/>
+  <xr:revisionPtr revIDLastSave="6506" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D66B42F3-48DF-48E9-9E6D-77DB609E0E8D}"/>
   <bookViews>
     <workbookView xWindow="10368" yWindow="1740" windowWidth="13908" windowHeight="9516" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="30">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -120,6 +120,9 @@
   </si>
   <si>
     <t>DCC</t>
+  </si>
+  <si>
+    <t>SCCC</t>
   </si>
 </sst>
 </file>
@@ -567,7 +570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="11.42578125" style="2" customWidth="1"/>
@@ -1813,7 +1816,7 @@
         <v>60116.55</v>
       </c>
       <c r="F59" s="6">
-        <f t="shared" ref="F59:F61" si="15">F58-D59+E59</f>
+        <f t="shared" ref="F59:F62" si="15">F58-D59+E59</f>
         <v>449633.46000000153</v>
       </c>
     </row>
@@ -1857,6 +1860,111 @@
       <c r="F61" s="14">
         <f t="shared" si="15"/>
         <v>399618.48000000155</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="15" customHeight="1">
+      <c r="A62" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B62" s="3">
+        <v>44968</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D62" s="8">
+        <v>20</v>
+      </c>
+      <c r="E62" s="8">
+        <v>0</v>
+      </c>
+      <c r="F62" s="6">
+        <f t="shared" si="15"/>
+        <v>399598.48000000155</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="15" customHeight="1">
+      <c r="A63" s="3">
+        <v>44970</v>
+      </c>
+      <c r="B63" s="3">
+        <v>44972</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D63" s="9">
+        <v>0</v>
+      </c>
+      <c r="E63" s="9">
+        <v>189778.73</v>
+      </c>
+      <c r="F63" s="6">
+        <f t="shared" ref="F63:F66" si="16">F62-D63+E63</f>
+        <v>589377.21000000159</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="15" customHeight="1">
+      <c r="A64" s="3">
+        <v>44970</v>
+      </c>
+      <c r="B64" s="3">
+        <v>44972</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D64" s="8">
+        <v>14.98</v>
+      </c>
+      <c r="E64" s="8">
+        <v>0</v>
+      </c>
+      <c r="F64" s="6">
+        <f t="shared" si="16"/>
+        <v>589362.23000000161</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="15" customHeight="1">
+      <c r="A65" s="3">
+        <v>44970</v>
+      </c>
+      <c r="B65" s="3">
+        <v>44972</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D65" s="9">
+        <v>45099.67</v>
+      </c>
+      <c r="E65" s="9">
+        <v>0</v>
+      </c>
+      <c r="F65" s="6">
+        <f t="shared" si="16"/>
+        <v>544262.56000000157</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="15" customHeight="1">
+      <c r="A66" s="3">
+        <v>44970</v>
+      </c>
+      <c r="B66" s="3">
+        <v>44972</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D66" s="8">
+        <v>14.98</v>
+      </c>
+      <c r="E66" s="8">
+        <v>0</v>
+      </c>
+      <c r="F66" s="6">
+        <f t="shared" si="16"/>
+        <v>544247.58000000159</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6506" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D66B42F3-48DF-48E9-9E6D-77DB609E0E8D}"/>
+  <xr:revisionPtr revIDLastSave="6518" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F3AB4D1-4D28-4584-9CB1-A6C1DB60081B}"/>
   <bookViews>
     <workbookView xWindow="10368" yWindow="1740" windowWidth="13908" windowHeight="9516" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="31">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -123,6 +123,9 @@
   </si>
   <si>
     <t>SCCC</t>
+  </si>
+  <si>
+    <t>JMART</t>
   </si>
 </sst>
 </file>
@@ -570,7 +573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="11.42578125" style="2" customWidth="1"/>
@@ -1967,6 +1970,90 @@
         <v>544247.58000000159</v>
       </c>
     </row>
+    <row r="67" spans="1:6" ht="15" customHeight="1">
+      <c r="A67" s="3">
+        <v>44972</v>
+      </c>
+      <c r="B67" s="3">
+        <v>44974</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D67" s="9">
+        <v>36681.06</v>
+      </c>
+      <c r="E67" s="9">
+        <v>0</v>
+      </c>
+      <c r="F67" s="6">
+        <f t="shared" ref="F67" si="17">F66-D67+E67</f>
+        <v>507566.52000000159</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="15" customHeight="1">
+      <c r="A68" s="3">
+        <v>44972</v>
+      </c>
+      <c r="B68" s="3">
+        <v>44974</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D68" s="9">
+        <v>25255.81</v>
+      </c>
+      <c r="E68" s="9">
+        <v>0</v>
+      </c>
+      <c r="F68" s="6">
+        <f t="shared" ref="F68" si="18">F67-D68+E68</f>
+        <v>482310.71000000159</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="15" customHeight="1">
+      <c r="A69" s="3">
+        <v>44972</v>
+      </c>
+      <c r="B69" s="3">
+        <v>44974</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D69" s="9">
+        <v>22850.5</v>
+      </c>
+      <c r="E69" s="9">
+        <v>0</v>
+      </c>
+      <c r="F69" s="6">
+        <f t="shared" ref="F69:F70" si="19">F68-D69+E69</f>
+        <v>459460.21000000159</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="15" customHeight="1">
+      <c r="A70" s="3">
+        <v>44972</v>
+      </c>
+      <c r="B70" s="3">
+        <v>44974</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D70" s="8">
+        <v>14.98</v>
+      </c>
+      <c r="E70" s="8">
+        <v>0</v>
+      </c>
+      <c r="F70" s="6">
+        <f t="shared" si="19"/>
+        <v>459445.23000000161</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6518" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F3AB4D1-4D28-4584-9CB1-A6C1DB60081B}"/>
+  <xr:revisionPtr revIDLastSave="6529" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB75F0BA-8B78-4EE6-8E6A-8FA32619603F}"/>
   <bookViews>
     <workbookView xWindow="10368" yWindow="1740" windowWidth="13908" windowHeight="9516" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="32">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -126,6 +126,9 @@
   </si>
   <si>
     <t>JMART</t>
+  </si>
+  <si>
+    <t>ASK</t>
   </si>
 </sst>
 </file>
@@ -573,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="11.42578125" style="2" customWidth="1"/>
@@ -1903,7 +1906,7 @@
         <v>189778.73</v>
       </c>
       <c r="F63" s="6">
-        <f t="shared" ref="F63:F66" si="16">F62-D63+E63</f>
+        <f t="shared" ref="F63:F71" si="16">F62-D63+E63</f>
         <v>589377.21000000159</v>
       </c>
     </row>
@@ -1971,24 +1974,24 @@
       </c>
     </row>
     <row r="67" spans="1:6" ht="15" customHeight="1">
-      <c r="A67" s="3">
+      <c r="A67" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B67" s="3">
         <v>44972</v>
       </c>
-      <c r="B67" s="3">
-        <v>44974</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D67" s="9">
-        <v>36681.06</v>
-      </c>
-      <c r="E67" s="9">
+      <c r="C67" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D67" s="8">
+        <v>432</v>
+      </c>
+      <c r="E67" s="8">
         <v>0</v>
       </c>
       <c r="F67" s="6">
-        <f t="shared" ref="F67" si="17">F66-D67+E67</f>
-        <v>507566.52000000159</v>
+        <f t="shared" si="16"/>
+        <v>543815.58000000159</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="15" customHeight="1">
@@ -1999,17 +2002,17 @@
         <v>44974</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D68" s="9">
-        <v>25255.81</v>
+        <v>36681.06</v>
       </c>
       <c r="E68" s="9">
         <v>0</v>
       </c>
       <c r="F68" s="6">
-        <f t="shared" ref="F68" si="18">F67-D68+E68</f>
-        <v>482310.71000000159</v>
+        <f t="shared" si="16"/>
+        <v>507134.52000000159</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1">
@@ -2023,14 +2026,14 @@
         <v>12</v>
       </c>
       <c r="D69" s="9">
-        <v>22850.5</v>
+        <v>25255.81</v>
       </c>
       <c r="E69" s="9">
         <v>0</v>
       </c>
       <c r="F69" s="6">
-        <f t="shared" ref="F69:F70" si="19">F68-D69+E69</f>
-        <v>459460.21000000159</v>
+        <f t="shared" si="16"/>
+        <v>481878.71000000159</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1">
@@ -2040,18 +2043,81 @@
       <c r="B70" s="3">
         <v>44974</v>
       </c>
-      <c r="C70" s="7" t="s">
+      <c r="C70" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D70" s="9">
+        <v>22850.5</v>
+      </c>
+      <c r="E70" s="9">
+        <v>0</v>
+      </c>
+      <c r="F70" s="6">
+        <f t="shared" si="16"/>
+        <v>459028.21000000159</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="15" customHeight="1">
+      <c r="A71" s="3">
+        <v>44972</v>
+      </c>
+      <c r="B71" s="3">
+        <v>44974</v>
+      </c>
+      <c r="C71" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D70" s="8">
+      <c r="D71" s="8">
         <v>14.98</v>
       </c>
-      <c r="E70" s="8">
-        <v>0</v>
-      </c>
-      <c r="F70" s="6">
-        <f t="shared" si="19"/>
-        <v>459445.23000000161</v>
+      <c r="E71" s="8">
+        <v>0</v>
+      </c>
+      <c r="F71" s="6">
+        <f t="shared" si="16"/>
+        <v>459013.23000000161</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="15" customHeight="1">
+      <c r="A72" s="3">
+        <v>44973</v>
+      </c>
+      <c r="B72" s="3">
+        <v>44977</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D72" s="9">
+        <v>139808.98000000001</v>
+      </c>
+      <c r="E72" s="9">
+        <v>0</v>
+      </c>
+      <c r="F72" s="6">
+        <f t="shared" ref="F72:F73" si="17">F71-D72+E72</f>
+        <v>319204.25000000163</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="15" customHeight="1">
+      <c r="A73" s="3">
+        <v>44973</v>
+      </c>
+      <c r="B73" s="3">
+        <v>44977</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D73" s="8">
+        <v>14.98</v>
+      </c>
+      <c r="E73" s="8">
+        <v>0</v>
+      </c>
+      <c r="F73" s="6">
+        <f t="shared" si="17"/>
+        <v>319189.27000000165</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26212"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26301"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6529" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB75F0BA-8B78-4EE6-8E6A-8FA32619603F}"/>
+  <xr:revisionPtr revIDLastSave="6540" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30D8C45A-FAD6-45C6-A49B-E9E7A915CC2D}"/>
   <bookViews>
     <workbookView xWindow="10368" yWindow="1740" windowWidth="13908" windowHeight="9516" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="32">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -140,7 +140,7 @@
     <numFmt numFmtId="188" formatCode="\฿#,##0.00"/>
     <numFmt numFmtId="189" formatCode="&quot;฿&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -201,6 +201,11 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -222,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -238,6 +243,7 @@
     <xf numFmtId="189" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="188" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -576,7 +582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="11.42578125" style="2" customWidth="1"/>
@@ -2100,10 +2106,10 @@
       </c>
     </row>
     <row r="73" spans="1:6" ht="15" customHeight="1">
-      <c r="A73" s="3">
+      <c r="A73" s="15">
         <v>44973</v>
       </c>
-      <c r="B73" s="3">
+      <c r="B73" s="15">
         <v>44977</v>
       </c>
       <c r="C73" s="7" t="s">
@@ -2118,6 +2124,69 @@
       <c r="F73" s="6">
         <f t="shared" si="17"/>
         <v>319189.27000000165</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="15" customHeight="1">
+      <c r="A74" s="3">
+        <v>44986</v>
+      </c>
+      <c r="B74" s="3">
+        <v>44988</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D74" s="9">
+        <v>164364.64744000003</v>
+      </c>
+      <c r="E74" s="9">
+        <v>0</v>
+      </c>
+      <c r="F74" s="6">
+        <f t="shared" ref="F74:F76" si="18">F73-D74+E74</f>
+        <v>154824.62256000162</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="15" customHeight="1">
+      <c r="A75" s="3">
+        <v>44986</v>
+      </c>
+      <c r="B75" s="3">
+        <v>44988</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D75" s="8">
+        <v>14.98</v>
+      </c>
+      <c r="E75" s="8">
+        <v>0</v>
+      </c>
+      <c r="F75" s="6">
+        <f t="shared" si="18"/>
+        <v>154809.64256000161</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="15" customHeight="1">
+      <c r="A76" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B76" s="3">
+        <v>44989</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D76" s="8">
+        <v>1320</v>
+      </c>
+      <c r="E76" s="8">
+        <v>0</v>
+      </c>
+      <c r="F76" s="6">
+        <f t="shared" si="18"/>
+        <v>153489.64256000161</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26301"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26306"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A7/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6540" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30D8C45A-FAD6-45C6-A49B-E9E7A915CC2D}"/>
+  <xr:revisionPtr revIDLastSave="6574" documentId="11_59254FB3F4AABE3ADC949A5AB88E13345563F2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20C7EA46-0492-419C-9DB7-7C6834DF1D97}"/>
   <bookViews>
     <workbookView xWindow="10368" yWindow="1740" windowWidth="13908" windowHeight="9516" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="35">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -129,6 +129,15 @@
   </si>
   <si>
     <t>ASK</t>
+  </si>
+  <si>
+    <t>DIF-DIV</t>
+  </si>
+  <si>
+    <t>DIF</t>
+  </si>
+  <si>
+    <t>GVREIT-DIV</t>
   </si>
 </sst>
 </file>
@@ -140,71 +149,36 @@
     <numFmt numFmtId="188" formatCode="\฿#,##0.00"/>
     <numFmt numFmtId="189" formatCode="&quot;฿&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="6">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Cordia New"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="14"/>
       <color rgb="FF000000"/>
-      <name val="Cordia New"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="14"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica Neue"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="14"/>
       <color rgb="FF333333"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="14"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Cordia New"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Cordia New"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -227,23 +201,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="189" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="187" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="189" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="189" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="189" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="188" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -582,1611 +551,1800 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="11.42578125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" style="1" customWidth="1"/>
-    <col min="7" max="11" width="10.140625" style="2"/>
-    <col min="12" max="12" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="10.140625" style="2"/>
+    <col min="1" max="2" width="14.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="10.140625" style="3"/>
+    <col min="12" max="12" width="10.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="10.140625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1">
-      <c r="A1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="11" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="4">
         <v>44927</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="6">
         <v>1310</v>
       </c>
-      <c r="E2" s="8">
-        <v>0</v>
-      </c>
-      <c r="F2" s="14">
+      <c r="E2" s="6">
+        <v>0</v>
+      </c>
+      <c r="F2" s="7">
         <v>214038.73000000126</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="4">
         <v>44930</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="6">
         <v>1900</v>
       </c>
-      <c r="E3" s="8">
-        <v>0</v>
-      </c>
-      <c r="F3" s="14">
+      <c r="E3" s="6">
+        <v>0</v>
+      </c>
+      <c r="F3" s="7">
         <f t="shared" ref="F3" si="0">F2-D3+E3</f>
         <v>212138.73000000126</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1">
-      <c r="A4" s="3">
+      <c r="A4" s="4">
         <v>44925</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="4">
         <v>44930</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="9">
-        <v>0</v>
-      </c>
-      <c r="E4" s="9">
+      <c r="D4" s="8">
+        <v>0</v>
+      </c>
+      <c r="E4" s="8">
         <v>49390.36</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="9">
         <f>F3-D4+E4</f>
         <v>261529.09000000125</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1">
-      <c r="A5" s="3">
+      <c r="A5" s="4">
         <v>44925</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="4">
         <v>44930</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="8">
-        <v>14.98</v>
-      </c>
-      <c r="E5" s="8">
-        <v>0</v>
-      </c>
-      <c r="F5" s="14">
+      <c r="C5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="6">
+        <v>14.98</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0</v>
+      </c>
+      <c r="F5" s="7">
         <f t="shared" ref="F5" si="1">F4-D5+E5</f>
         <v>261514.11000000124</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1">
-      <c r="A6" s="3">
+      <c r="A6" s="4">
         <v>44929</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="4">
         <v>44931</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="9">
-        <v>0</v>
-      </c>
-      <c r="E6" s="9">
+      <c r="D6" s="8">
+        <v>0</v>
+      </c>
+      <c r="E6" s="8">
         <v>98032.38</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="9">
         <f t="shared" ref="F6:F7" si="2">F5-D6+E6</f>
         <v>359546.49000000127</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1">
-      <c r="A7" s="3">
+      <c r="A7" s="4">
         <v>44929</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="4">
         <v>44931</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="8">
-        <v>14.98</v>
-      </c>
-      <c r="E7" s="8">
-        <v>0</v>
-      </c>
-      <c r="F7" s="14">
+      <c r="C7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="6">
+        <v>14.98</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0</v>
+      </c>
+      <c r="F7" s="7">
         <f t="shared" si="2"/>
         <v>359531.51000000129</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1">
-      <c r="A8" s="3">
+      <c r="A8" s="4">
         <v>44930</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="4">
         <v>44932</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="8">
         <v>99219.28</v>
       </c>
-      <c r="E8" s="9">
-        <v>0</v>
-      </c>
-      <c r="F8" s="6">
+      <c r="E8" s="8">
+        <v>0</v>
+      </c>
+      <c r="F8" s="9">
         <f t="shared" ref="F8:F9" si="3">F7-D8+E8</f>
         <v>260312.23000000129</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1">
-      <c r="A9" s="3">
+      <c r="A9" s="4">
         <v>44930</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="4">
         <v>44932</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="8">
-        <v>14.98</v>
-      </c>
-      <c r="E9" s="8">
-        <v>0</v>
-      </c>
-      <c r="F9" s="14">
+      <c r="C9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="6">
+        <v>14.98</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0</v>
+      </c>
+      <c r="F9" s="7">
         <f t="shared" si="3"/>
         <v>260297.25000000128</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1">
-      <c r="A10" s="3">
+      <c r="A10" s="4">
         <v>44932</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="4">
         <v>44936</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="8">
         <v>147926.92000000001</v>
       </c>
-      <c r="E10" s="9">
-        <v>0</v>
-      </c>
-      <c r="F10" s="6">
+      <c r="E10" s="8">
+        <v>0</v>
+      </c>
+      <c r="F10" s="9">
         <f t="shared" ref="F10:F12" si="4">F9-D10+E10</f>
         <v>112370.33000000127</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1">
-      <c r="A11" s="3">
+      <c r="A11" s="4">
         <v>44932</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="4">
         <v>44936</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="8">
-        <v>14.98</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0</v>
-      </c>
-      <c r="F11" s="14">
+      <c r="C11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="6">
+        <v>14.98</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0</v>
+      </c>
+      <c r="F11" s="7">
         <f t="shared" si="4"/>
         <v>112355.35000000127</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1">
-      <c r="A12" s="3">
+      <c r="A12" s="4">
         <v>44935</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="4">
         <v>44937</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="9">
-        <v>0</v>
-      </c>
-      <c r="E12" s="9">
+      <c r="D12" s="8">
+        <v>0</v>
+      </c>
+      <c r="E12" s="8">
         <v>125720.92</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="9">
         <f t="shared" si="4"/>
         <v>238076.27000000127</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1">
-      <c r="A13" s="3">
+      <c r="A13" s="4">
         <v>44935</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="4">
         <v>44937</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="9">
-        <v>0</v>
-      </c>
-      <c r="E13" s="9">
+      <c r="D13" s="8">
+        <v>0</v>
+      </c>
+      <c r="E13" s="8">
         <v>105066.77</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="9">
         <f t="shared" ref="F13:F14" si="5">F12-D13+E13</f>
         <v>343143.04000000126</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1">
-      <c r="A14" s="3">
+      <c r="A14" s="4">
         <v>44935</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="4">
         <v>44937</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="8">
-        <v>14.98</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0</v>
-      </c>
-      <c r="F14" s="14">
+      <c r="C14" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="6">
+        <v>14.98</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0</v>
+      </c>
+      <c r="F14" s="7">
         <f t="shared" si="5"/>
         <v>343128.06000000128</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="4">
         <v>44940</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="6">
         <v>20</v>
       </c>
-      <c r="E15" s="8">
-        <v>0</v>
-      </c>
-      <c r="F15" s="14">
+      <c r="E15" s="6">
+        <v>0</v>
+      </c>
+      <c r="F15" s="7">
         <f t="shared" ref="F15" si="6">F14-D15+E15</f>
         <v>343108.06000000128</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="4">
         <v>44941</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="6">
         <v>225</v>
       </c>
-      <c r="E16" s="8">
-        <v>0</v>
-      </c>
-      <c r="F16" s="14">
+      <c r="E16" s="6">
+        <v>0</v>
+      </c>
+      <c r="F16" s="7">
         <f>F15-D16+E16</f>
         <v>342883.06000000128</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="4">
         <v>44942</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="6">
         <v>240</v>
       </c>
-      <c r="E17" s="8">
-        <v>0</v>
-      </c>
-      <c r="F17" s="14">
+      <c r="E17" s="6">
+        <v>0</v>
+      </c>
+      <c r="F17" s="7">
         <f>F16-D17+E17</f>
         <v>342643.06000000128</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="4">
         <v>44945</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="8">
-        <v>0</v>
-      </c>
-      <c r="E18" s="8">
+      <c r="D18" s="6">
+        <v>0</v>
+      </c>
+      <c r="E18" s="6">
         <v>304081.40000000002</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="7">
         <f t="shared" ref="F18:F26" si="7">F17-D18+E18</f>
         <v>646724.46000000136</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1">
-      <c r="A19" s="3">
+      <c r="A19" s="4">
         <v>44943</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="4">
         <v>44945</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="9">
-        <v>0</v>
-      </c>
-      <c r="E19" s="9">
+      <c r="D19" s="8">
+        <v>0</v>
+      </c>
+      <c r="E19" s="8">
         <v>151912.78</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="9">
         <f t="shared" si="7"/>
         <v>798637.24000000139</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" customHeight="1">
-      <c r="A20" s="3">
+      <c r="A20" s="4">
         <v>44943</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="4">
         <v>44945</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="8">
         <v>89197.13</v>
       </c>
-      <c r="E20" s="9">
-        <v>0</v>
-      </c>
-      <c r="F20" s="6">
+      <c r="E20" s="8">
+        <v>0</v>
+      </c>
+      <c r="F20" s="9">
         <f t="shared" si="7"/>
         <v>709440.11000000138</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15" customHeight="1">
-      <c r="A21" s="3">
+      <c r="A21" s="4">
         <v>44943</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="4">
         <v>44945</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="8">
-        <v>14.98</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0</v>
-      </c>
-      <c r="F21" s="14">
+      <c r="C21" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="6">
+        <v>14.98</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0</v>
+      </c>
+      <c r="F21" s="7">
         <f t="shared" si="7"/>
         <v>709425.1300000014</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15" customHeight="1">
-      <c r="A22" s="3">
+      <c r="A22" s="4">
         <v>44944</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="4">
         <v>44946</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="8">
         <v>89197.13</v>
       </c>
-      <c r="E22" s="9">
-        <v>0</v>
-      </c>
-      <c r="F22" s="6">
+      <c r="E22" s="8">
+        <v>0</v>
+      </c>
+      <c r="F22" s="9">
         <f t="shared" si="7"/>
         <v>620228.0000000014</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1">
-      <c r="A23" s="3">
+      <c r="A23" s="4">
         <v>44944</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="4">
         <v>44946</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="8">
-        <v>14.98</v>
-      </c>
-      <c r="E23" s="8">
-        <v>0</v>
-      </c>
-      <c r="F23" s="14">
+      <c r="C23" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="6">
+        <v>14.98</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0</v>
+      </c>
+      <c r="F23" s="7">
         <f t="shared" si="7"/>
         <v>620213.02000000142</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1">
-      <c r="A24" s="3">
+      <c r="A24" s="4">
         <v>44945</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="4">
         <v>45100</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="8">
         <v>101023.27</v>
       </c>
-      <c r="E24" s="9">
-        <v>0</v>
-      </c>
-      <c r="F24" s="6">
+      <c r="E24" s="8">
+        <v>0</v>
+      </c>
+      <c r="F24" s="9">
         <f t="shared" si="7"/>
         <v>519189.7500000014</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1">
-      <c r="A25" s="3">
+      <c r="A25" s="4">
         <v>44945</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="4">
         <v>45100</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D25" s="9">
-        <v>0</v>
-      </c>
-      <c r="E25" s="9">
+      <c r="D25" s="8">
+        <v>0</v>
+      </c>
+      <c r="E25" s="8">
         <v>52882.61</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F25" s="9">
         <f t="shared" si="7"/>
         <v>572072.36000000138</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" customHeight="1">
-      <c r="A26" s="3">
+      <c r="A26" s="4">
         <v>44945</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="4">
         <v>45100</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="8">
-        <v>14.98</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0</v>
-      </c>
-      <c r="F26" s="6">
+      <c r="C26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="6">
+        <v>14.98</v>
+      </c>
+      <c r="E26" s="6">
+        <v>0</v>
+      </c>
+      <c r="F26" s="9">
         <f t="shared" si="7"/>
         <v>572057.3800000014</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" customHeight="1">
-      <c r="A27" s="3">
+      <c r="A27" s="4">
         <v>44946</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="4">
         <v>44950</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="9">
+      <c r="D27" s="8">
         <v>142514.95000000001</v>
       </c>
-      <c r="E27" s="9">
-        <v>0</v>
-      </c>
-      <c r="F27" s="6">
+      <c r="E27" s="8">
+        <v>0</v>
+      </c>
+      <c r="F27" s="9">
         <f t="shared" ref="F27:F29" si="8">F26-D27+E27</f>
         <v>429542.43000000139</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1">
-      <c r="A28" s="3">
+      <c r="A28" s="4">
         <v>44946</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="4">
         <v>44950</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="8">
-        <v>14.98</v>
-      </c>
-      <c r="E28" s="8">
-        <v>0</v>
-      </c>
-      <c r="F28" s="6">
+      <c r="C28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="6">
+        <v>14.98</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0</v>
+      </c>
+      <c r="F28" s="9">
         <f t="shared" si="8"/>
         <v>429527.45000000141</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="4">
         <v>44950</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="6">
         <v>29500</v>
       </c>
-      <c r="E29" s="8">
-        <v>0</v>
-      </c>
-      <c r="F29" s="6">
+      <c r="E29" s="6">
+        <v>0</v>
+      </c>
+      <c r="F29" s="9">
         <f t="shared" si="8"/>
         <v>400027.45000000141</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" customHeight="1">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="4">
         <v>44951</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D30" s="8">
-        <v>0</v>
-      </c>
-      <c r="E30" s="8">
+      <c r="D30" s="6">
+        <v>0</v>
+      </c>
+      <c r="E30" s="6">
         <v>102052.5</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F30" s="9">
         <f t="shared" ref="F30:F36" si="9">F29-D30+E30</f>
         <v>502079.95000000141</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1">
-      <c r="A31" s="3">
+      <c r="A31" s="4">
         <v>44950</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31" s="4">
         <v>44952</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D31" s="9">
-        <v>0</v>
-      </c>
-      <c r="E31" s="9">
+      <c r="D31" s="8">
+        <v>0</v>
+      </c>
+      <c r="E31" s="8">
         <v>318044</v>
       </c>
-      <c r="F31" s="6">
+      <c r="F31" s="9">
         <f t="shared" si="9"/>
         <v>820123.95000000135</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15" customHeight="1">
-      <c r="A32" s="3">
+      <c r="A32" s="4">
         <v>44950</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="4">
         <v>44952</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D32" s="9">
+      <c r="D32" s="8">
         <v>195431.91</v>
       </c>
-      <c r="E32" s="9">
-        <v>0</v>
-      </c>
-      <c r="F32" s="6">
+      <c r="E32" s="8">
+        <v>0</v>
+      </c>
+      <c r="F32" s="9">
         <f t="shared" si="9"/>
         <v>624692.04000000132</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15" customHeight="1">
-      <c r="A33" s="3">
+      <c r="A33" s="4">
         <v>44950</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B33" s="4">
         <v>44952</v>
       </c>
-      <c r="C33" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D33" s="8">
-        <v>14.98</v>
-      </c>
-      <c r="E33" s="8">
-        <v>0</v>
-      </c>
-      <c r="F33" s="6">
+      <c r="C33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" s="6">
+        <v>14.98</v>
+      </c>
+      <c r="E33" s="6">
+        <v>0</v>
+      </c>
+      <c r="F33" s="9">
         <f t="shared" si="9"/>
         <v>624677.06000000134</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1">
-      <c r="A34" s="3">
+      <c r="A34" s="4">
         <v>44951</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B34" s="4">
         <v>44953</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D34" s="9">
-        <v>0</v>
-      </c>
-      <c r="E34" s="9">
+      <c r="D34" s="8">
+        <v>0</v>
+      </c>
+      <c r="E34" s="8">
         <v>53381.5</v>
       </c>
-      <c r="F34" s="6">
+      <c r="F34" s="9">
         <f t="shared" si="9"/>
         <v>678058.56000000134</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1">
-      <c r="A35" s="3">
+      <c r="A35" s="4">
         <v>44951</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35" s="4">
         <v>44953</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D35" s="9">
-        <v>0</v>
-      </c>
-      <c r="E35" s="9">
+      <c r="D35" s="8">
+        <v>0</v>
+      </c>
+      <c r="E35" s="8">
         <v>54628.74</v>
       </c>
-      <c r="F35" s="6">
+      <c r="F35" s="9">
         <f t="shared" si="9"/>
         <v>732687.30000000133</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1">
-      <c r="A36" s="3">
+      <c r="A36" s="4">
         <v>44951</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36" s="4">
         <v>44953</v>
       </c>
-      <c r="C36" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36" s="8">
-        <v>14.98</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0</v>
-      </c>
-      <c r="F36" s="14">
+      <c r="C36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" s="6">
+        <v>14.98</v>
+      </c>
+      <c r="E36" s="6">
+        <v>0</v>
+      </c>
+      <c r="F36" s="7">
         <f t="shared" si="9"/>
         <v>732672.32000000135</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15" customHeight="1">
-      <c r="A37" s="3">
+      <c r="A37" s="4">
         <v>44952</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B37" s="4">
         <v>44956</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D37" s="9">
+      <c r="D37" s="8">
         <v>140710.97</v>
       </c>
-      <c r="E37" s="9">
-        <v>0</v>
-      </c>
-      <c r="F37" s="6">
+      <c r="E37" s="8">
+        <v>0</v>
+      </c>
+      <c r="F37" s="9">
         <f t="shared" ref="F37" si="10">F36-D37+E37</f>
         <v>591961.35000000137</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1">
-      <c r="A38" s="3">
+      <c r="A38" s="4">
         <v>44952</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B38" s="4">
         <v>44956</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D38" s="8">
         <v>96212.63</v>
       </c>
-      <c r="E38" s="9">
-        <v>0</v>
-      </c>
-      <c r="F38" s="6">
+      <c r="E38" s="8">
+        <v>0</v>
+      </c>
+      <c r="F38" s="9">
         <f t="shared" ref="F38:F53" si="11">F37-D38+E38</f>
         <v>495748.72000000137</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15" customHeight="1">
-      <c r="A39" s="3">
+      <c r="A39" s="4">
         <v>44952</v>
       </c>
-      <c r="B39" s="3">
+      <c r="B39" s="4">
         <v>44956</v>
       </c>
-      <c r="C39" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D39" s="8">
-        <v>14.98</v>
-      </c>
-      <c r="E39" s="8">
-        <v>0</v>
-      </c>
-      <c r="F39" s="6">
+      <c r="C39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" s="6">
+        <v>14.98</v>
+      </c>
+      <c r="E39" s="6">
+        <v>0</v>
+      </c>
+      <c r="F39" s="9">
         <f t="shared" si="11"/>
         <v>495733.74000000139</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B40" s="3">
+      <c r="B40" s="4">
         <v>44957</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D40" s="8">
+      <c r="D40" s="6">
         <v>27200</v>
       </c>
-      <c r="E40" s="8">
-        <v>0</v>
-      </c>
-      <c r="F40" s="6">
+      <c r="E40" s="6">
+        <v>0</v>
+      </c>
+      <c r="F40" s="9">
         <f t="shared" si="11"/>
         <v>468533.74000000139</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1">
-      <c r="A41" s="3">
+      <c r="A41" s="4">
         <v>44956</v>
       </c>
-      <c r="B41" s="3">
+      <c r="B41" s="4">
         <v>44958</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D41" s="9">
+      <c r="D41" s="8">
         <v>77170.55</v>
       </c>
-      <c r="E41" s="9">
-        <v>0</v>
-      </c>
-      <c r="F41" s="6">
+      <c r="E41" s="8">
+        <v>0</v>
+      </c>
+      <c r="F41" s="9">
         <f t="shared" si="11"/>
         <v>391363.1900000014</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15" customHeight="1">
-      <c r="A42" s="3">
+      <c r="A42" s="4">
         <v>44956</v>
       </c>
-      <c r="B42" s="3">
+      <c r="B42" s="4">
         <v>44958</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D42" s="9">
+      <c r="D42" s="8">
         <v>77170.55</v>
       </c>
-      <c r="E42" s="9">
-        <v>0</v>
-      </c>
-      <c r="F42" s="6">
+      <c r="E42" s="8">
+        <v>0</v>
+      </c>
+      <c r="F42" s="9">
         <f t="shared" si="11"/>
         <v>314192.64000000141</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15" customHeight="1">
-      <c r="A43" s="3">
+      <c r="A43" s="4">
         <v>44956</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B43" s="4">
         <v>44958</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D43" s="9">
+      <c r="D43" s="8">
         <v>47805.65</v>
       </c>
-      <c r="E43" s="9">
-        <v>0</v>
-      </c>
-      <c r="F43" s="6">
+      <c r="E43" s="8">
+        <v>0</v>
+      </c>
+      <c r="F43" s="9">
         <f t="shared" si="11"/>
         <v>266386.99000000139</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15" customHeight="1">
-      <c r="A44" s="3">
+      <c r="A44" s="4">
         <v>44956</v>
       </c>
-      <c r="B44" s="3">
+      <c r="B44" s="4">
         <v>44958</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D44" s="9">
-        <v>0</v>
-      </c>
-      <c r="E44" s="9">
+      <c r="D44" s="8">
+        <v>0</v>
+      </c>
+      <c r="E44" s="8">
         <v>77827.240000000005</v>
       </c>
-      <c r="F44" s="6">
+      <c r="F44" s="9">
         <f t="shared" si="11"/>
         <v>344214.23000000138</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15" customHeight="1">
-      <c r="A45" s="3">
+      <c r="A45" s="4">
         <v>44956</v>
       </c>
-      <c r="B45" s="3">
+      <c r="B45" s="4">
         <v>44958</v>
       </c>
-      <c r="C45" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D45" s="8">
-        <v>14.98</v>
-      </c>
-      <c r="E45" s="8">
-        <v>0</v>
-      </c>
-      <c r="F45" s="6">
+      <c r="C45" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" s="6">
+        <v>14.98</v>
+      </c>
+      <c r="E45" s="6">
+        <v>0</v>
+      </c>
+      <c r="F45" s="9">
         <f t="shared" si="11"/>
         <v>344199.2500000014</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B46" s="3">
+      <c r="B46" s="4">
         <v>44958</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D46" s="8">
+      <c r="D46" s="6">
         <v>1200</v>
       </c>
-      <c r="E46" s="8">
-        <v>0</v>
-      </c>
-      <c r="F46" s="14">
+      <c r="E46" s="6">
+        <v>0</v>
+      </c>
+      <c r="F46" s="7">
         <f t="shared" si="11"/>
         <v>342999.2500000014</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1">
-      <c r="A47" s="3">
+      <c r="A47" s="4">
         <v>44957</v>
       </c>
-      <c r="B47" s="3">
+      <c r="B47" s="4">
         <v>44959</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D47" s="9">
-        <v>0</v>
-      </c>
-      <c r="E47" s="9">
+      <c r="D47" s="8">
+        <v>0</v>
+      </c>
+      <c r="E47" s="8">
         <v>53630.95</v>
       </c>
-      <c r="F47" s="6">
+      <c r="F47" s="9">
         <f t="shared" si="11"/>
         <v>396630.20000000141</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15" customHeight="1">
-      <c r="A48" s="3">
+      <c r="A48" s="4">
         <v>44957</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B48" s="4">
         <v>44959</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D48" s="9">
+      <c r="D48" s="8">
         <v>68551.5</v>
       </c>
-      <c r="E48" s="9">
-        <v>0</v>
-      </c>
-      <c r="F48" s="6">
+      <c r="E48" s="8">
+        <v>0</v>
+      </c>
+      <c r="F48" s="9">
         <f t="shared" si="11"/>
         <v>328078.70000000141</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15" customHeight="1">
-      <c r="A49" s="3">
+      <c r="A49" s="4">
         <v>44957</v>
       </c>
-      <c r="B49" s="3">
+      <c r="B49" s="4">
         <v>44959</v>
       </c>
-      <c r="C49" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D49" s="8">
-        <v>14.98</v>
-      </c>
-      <c r="E49" s="8">
-        <v>0</v>
-      </c>
-      <c r="F49" s="6">
+      <c r="C49" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" s="6">
+        <v>14.98</v>
+      </c>
+      <c r="E49" s="6">
+        <v>0</v>
+      </c>
+      <c r="F49" s="9">
         <f t="shared" si="11"/>
         <v>328063.72000000143</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15" customHeight="1">
-      <c r="A50" s="3">
+      <c r="A50" s="4">
         <v>44958</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B50" s="4">
         <v>44960</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D50" s="9">
-        <v>0</v>
-      </c>
-      <c r="E50" s="9">
+      <c r="D50" s="8">
+        <v>0</v>
+      </c>
+      <c r="E50" s="8">
         <v>55875.97</v>
       </c>
-      <c r="F50" s="6">
+      <c r="F50" s="9">
         <f t="shared" si="11"/>
         <v>383939.69000000146</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15" customHeight="1">
-      <c r="A51" s="3">
+      <c r="A51" s="4">
         <v>44958</v>
       </c>
-      <c r="B51" s="3">
+      <c r="B51" s="4">
         <v>44960</v>
       </c>
-      <c r="C51" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D51" s="8">
-        <v>14.98</v>
-      </c>
-      <c r="E51" s="8">
-        <v>0</v>
-      </c>
-      <c r="F51" s="6">
+      <c r="C51" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" s="6">
+        <v>14.98</v>
+      </c>
+      <c r="E51" s="6">
+        <v>0</v>
+      </c>
+      <c r="F51" s="9">
         <f t="shared" si="11"/>
         <v>383924.71000000148</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="15" customHeight="1">
-      <c r="A52" s="3">
+      <c r="A52" s="4">
         <v>44959</v>
       </c>
-      <c r="B52" s="3">
+      <c r="B52" s="4">
         <v>44963</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D52" s="9">
+      <c r="D52" s="8">
         <v>90951</v>
       </c>
-      <c r="E52" s="9">
-        <v>0</v>
-      </c>
-      <c r="F52" s="6">
+      <c r="E52" s="8">
+        <v>0</v>
+      </c>
+      <c r="F52" s="9">
         <f t="shared" si="11"/>
         <v>292973.71000000148</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15" customHeight="1">
-      <c r="A53" s="3">
+      <c r="A53" s="4">
         <v>44959</v>
       </c>
-      <c r="B53" s="3">
+      <c r="B53" s="4">
         <v>44963</v>
       </c>
-      <c r="C53" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D53" s="8">
-        <v>14.98</v>
-      </c>
-      <c r="E53" s="8">
-        <v>0</v>
-      </c>
-      <c r="F53" s="6">
+      <c r="C53" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="6">
+        <v>14.98</v>
+      </c>
+      <c r="E53" s="6">
+        <v>0</v>
+      </c>
+      <c r="F53" s="9">
         <f t="shared" si="11"/>
         <v>292958.73000000149</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15" customHeight="1">
-      <c r="A54" s="3">
+      <c r="A54" s="4">
         <v>44964</v>
       </c>
-      <c r="B54" s="3">
+      <c r="B54" s="4">
         <v>44966</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D54" s="9">
+      <c r="D54" s="8">
         <v>183405.33</v>
       </c>
-      <c r="E54" s="9">
-        <v>0</v>
-      </c>
-      <c r="F54" s="6">
+      <c r="E54" s="8">
+        <v>0</v>
+      </c>
+      <c r="F54" s="9">
         <f t="shared" ref="F54:F56" si="12">F53-D54+E54</f>
         <v>109553.40000000151</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15" customHeight="1">
-      <c r="A55" s="3">
+      <c r="A55" s="4">
         <v>44964</v>
       </c>
-      <c r="B55" s="3">
+      <c r="B55" s="4">
         <v>44966</v>
       </c>
-      <c r="C55" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D55" s="8">
-        <v>14.98</v>
-      </c>
-      <c r="E55" s="8">
-        <v>0</v>
-      </c>
-      <c r="F55" s="6">
+      <c r="C55" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D55" s="6">
+        <v>14.98</v>
+      </c>
+      <c r="E55" s="6">
+        <v>0</v>
+      </c>
+      <c r="F55" s="9">
         <f t="shared" si="12"/>
         <v>109538.42000000151</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15" customHeight="1">
-      <c r="A56" s="3">
+      <c r="A56" s="4">
         <v>44965</v>
       </c>
-      <c r="B56" s="3">
+      <c r="B56" s="4">
         <v>44967</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C56" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D56" s="9">
-        <v>0</v>
-      </c>
-      <c r="E56" s="9">
+      <c r="D56" s="8">
+        <v>0</v>
+      </c>
+      <c r="E56" s="8">
         <v>54379.28</v>
       </c>
-      <c r="F56" s="6">
+      <c r="F56" s="9">
         <f t="shared" si="12"/>
         <v>163917.70000000153</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1">
-      <c r="A57" s="3">
+      <c r="A57" s="4">
         <v>44965</v>
       </c>
-      <c r="B57" s="3">
+      <c r="B57" s="4">
         <v>44967</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C57" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D57" s="9">
-        <v>0</v>
-      </c>
-      <c r="E57" s="9">
+      <c r="D57" s="8">
+        <v>0</v>
+      </c>
+      <c r="E57" s="8">
         <v>54379.28</v>
       </c>
-      <c r="F57" s="6">
+      <c r="F57" s="9">
         <f t="shared" ref="F57" si="13">F56-D57+E57</f>
         <v>218296.98000000152</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1">
-      <c r="A58" s="3">
+      <c r="A58" s="4">
         <v>44965</v>
       </c>
-      <c r="B58" s="3">
+      <c r="B58" s="4">
         <v>44967</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C58" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D58" s="9">
-        <v>0</v>
-      </c>
-      <c r="E58" s="9">
+      <c r="D58" s="8">
+        <v>0</v>
+      </c>
+      <c r="E58" s="8">
         <v>171219.93</v>
       </c>
-      <c r="F58" s="6">
+      <c r="F58" s="9">
         <f t="shared" ref="F58" si="14">F57-D58+E58</f>
         <v>389516.91000000155</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15" customHeight="1">
-      <c r="A59" s="3">
+      <c r="A59" s="4">
         <v>44965</v>
       </c>
-      <c r="B59" s="3">
+      <c r="B59" s="4">
         <v>44967</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="C59" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D59" s="9">
-        <v>0</v>
-      </c>
-      <c r="E59" s="9">
+      <c r="D59" s="8">
+        <v>0</v>
+      </c>
+      <c r="E59" s="8">
         <v>60116.55</v>
       </c>
-      <c r="F59" s="6">
+      <c r="F59" s="9">
         <f t="shared" ref="F59:F62" si="15">F58-D59+E59</f>
         <v>449633.46000000153</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="15" customHeight="1">
-      <c r="A60" s="3">
+      <c r="A60" s="4">
         <v>44965</v>
       </c>
-      <c r="B60" s="3">
+      <c r="B60" s="4">
         <v>44967</v>
       </c>
-      <c r="C60" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D60" s="8">
-        <v>14.98</v>
-      </c>
-      <c r="E60" s="8">
-        <v>0</v>
-      </c>
-      <c r="F60" s="6">
+      <c r="C60" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D60" s="6">
+        <v>14.98</v>
+      </c>
+      <c r="E60" s="6">
+        <v>0</v>
+      </c>
+      <c r="F60" s="9">
         <f t="shared" si="15"/>
         <v>449618.48000000155</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="15" customHeight="1">
-      <c r="A61" s="3" t="s">
+      <c r="A61" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B61" s="3">
+      <c r="B61" s="4">
         <v>44967</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C61" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D61" s="8">
+      <c r="D61" s="6">
         <v>50000</v>
       </c>
-      <c r="E61" s="8">
-        <v>0</v>
-      </c>
-      <c r="F61" s="14">
+      <c r="E61" s="6">
+        <v>0</v>
+      </c>
+      <c r="F61" s="7">
         <f t="shared" si="15"/>
         <v>399618.48000000155</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="15" customHeight="1">
-      <c r="A62" s="3" t="s">
+      <c r="A62" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B62" s="3">
+      <c r="B62" s="4">
         <v>44968</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="C62" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D62" s="8">
+      <c r="D62" s="6">
         <v>20</v>
       </c>
-      <c r="E62" s="8">
-        <v>0</v>
-      </c>
-      <c r="F62" s="6">
+      <c r="E62" s="6">
+        <v>0</v>
+      </c>
+      <c r="F62" s="9">
         <f t="shared" si="15"/>
         <v>399598.48000000155</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15" customHeight="1">
-      <c r="A63" s="3">
+      <c r="A63" s="4">
         <v>44970</v>
       </c>
-      <c r="B63" s="3">
+      <c r="B63" s="4">
         <v>44972</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="C63" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D63" s="9">
-        <v>0</v>
-      </c>
-      <c r="E63" s="9">
+      <c r="D63" s="8">
+        <v>0</v>
+      </c>
+      <c r="E63" s="8">
         <v>189778.73</v>
       </c>
-      <c r="F63" s="6">
+      <c r="F63" s="9">
         <f t="shared" ref="F63:F71" si="16">F62-D63+E63</f>
         <v>589377.21000000159</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="15" customHeight="1">
-      <c r="A64" s="3">
+      <c r="A64" s="4">
         <v>44970</v>
       </c>
-      <c r="B64" s="3">
+      <c r="B64" s="4">
         <v>44972</v>
       </c>
-      <c r="C64" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D64" s="8">
-        <v>14.98</v>
-      </c>
-      <c r="E64" s="8">
-        <v>0</v>
-      </c>
-      <c r="F64" s="6">
+      <c r="C64" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D64" s="6">
+        <v>14.98</v>
+      </c>
+      <c r="E64" s="6">
+        <v>0</v>
+      </c>
+      <c r="F64" s="9">
         <f t="shared" si="16"/>
         <v>589362.23000000161</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="15" customHeight="1">
-      <c r="A65" s="3">
+      <c r="A65" s="4">
         <v>44970</v>
       </c>
-      <c r="B65" s="3">
+      <c r="B65" s="4">
         <v>44972</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C65" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D65" s="9">
+      <c r="D65" s="8">
         <v>45099.67</v>
       </c>
-      <c r="E65" s="9">
-        <v>0</v>
-      </c>
-      <c r="F65" s="6">
+      <c r="E65" s="8">
+        <v>0</v>
+      </c>
+      <c r="F65" s="9">
         <f t="shared" si="16"/>
         <v>544262.56000000157</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="15" customHeight="1">
-      <c r="A66" s="3">
+      <c r="A66" s="4">
         <v>44970</v>
       </c>
-      <c r="B66" s="3">
+      <c r="B66" s="4">
         <v>44972</v>
       </c>
-      <c r="C66" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D66" s="8">
-        <v>14.98</v>
-      </c>
-      <c r="E66" s="8">
-        <v>0</v>
-      </c>
-      <c r="F66" s="6">
+      <c r="C66" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D66" s="6">
+        <v>14.98</v>
+      </c>
+      <c r="E66" s="6">
+        <v>0</v>
+      </c>
+      <c r="F66" s="9">
         <f t="shared" si="16"/>
         <v>544247.58000000159</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="15" customHeight="1">
-      <c r="A67" s="3" t="s">
+      <c r="A67" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B67" s="3">
+      <c r="B67" s="4">
         <v>44972</v>
       </c>
-      <c r="C67" s="7" t="s">
+      <c r="C67" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D67" s="8">
+      <c r="D67" s="6">
         <v>432</v>
       </c>
-      <c r="E67" s="8">
-        <v>0</v>
-      </c>
-      <c r="F67" s="6">
+      <c r="E67" s="6">
+        <v>0</v>
+      </c>
+      <c r="F67" s="9">
         <f t="shared" si="16"/>
         <v>543815.58000000159</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="15" customHeight="1">
-      <c r="A68" s="3">
+      <c r="A68" s="4">
         <v>44972</v>
       </c>
-      <c r="B68" s="3">
+      <c r="B68" s="4">
         <v>44974</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="C68" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D68" s="9">
+      <c r="D68" s="8">
         <v>36681.06</v>
       </c>
-      <c r="E68" s="9">
-        <v>0</v>
-      </c>
-      <c r="F68" s="6">
+      <c r="E68" s="8">
+        <v>0</v>
+      </c>
+      <c r="F68" s="9">
         <f t="shared" si="16"/>
         <v>507134.52000000159</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1">
-      <c r="A69" s="3">
+      <c r="A69" s="4">
         <v>44972</v>
       </c>
-      <c r="B69" s="3">
+      <c r="B69" s="4">
         <v>44974</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="C69" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D69" s="9">
+      <c r="D69" s="8">
         <v>25255.81</v>
       </c>
-      <c r="E69" s="9">
-        <v>0</v>
-      </c>
-      <c r="F69" s="6">
+      <c r="E69" s="8">
+        <v>0</v>
+      </c>
+      <c r="F69" s="9">
         <f t="shared" si="16"/>
         <v>481878.71000000159</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1">
-      <c r="A70" s="3">
+      <c r="A70" s="4">
         <v>44972</v>
       </c>
-      <c r="B70" s="3">
+      <c r="B70" s="4">
         <v>44974</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="C70" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D70" s="9">
+      <c r="D70" s="8">
         <v>22850.5</v>
       </c>
-      <c r="E70" s="9">
-        <v>0</v>
-      </c>
-      <c r="F70" s="6">
+      <c r="E70" s="8">
+        <v>0</v>
+      </c>
+      <c r="F70" s="9">
         <f t="shared" si="16"/>
         <v>459028.21000000159</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="15" customHeight="1">
-      <c r="A71" s="3">
+      <c r="A71" s="4">
         <v>44972</v>
       </c>
-      <c r="B71" s="3">
+      <c r="B71" s="4">
         <v>44974</v>
       </c>
-      <c r="C71" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D71" s="8">
-        <v>14.98</v>
-      </c>
-      <c r="E71" s="8">
-        <v>0</v>
-      </c>
-      <c r="F71" s="6">
+      <c r="C71" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D71" s="6">
+        <v>14.98</v>
+      </c>
+      <c r="E71" s="6">
+        <v>0</v>
+      </c>
+      <c r="F71" s="9">
         <f t="shared" si="16"/>
         <v>459013.23000000161</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="15" customHeight="1">
-      <c r="A72" s="3">
+      <c r="A72" s="4">
         <v>44973</v>
       </c>
-      <c r="B72" s="3">
+      <c r="B72" s="4">
         <v>44977</v>
       </c>
-      <c r="C72" s="4" t="s">
+      <c r="C72" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D72" s="9">
+      <c r="D72" s="8">
         <v>139808.98000000001</v>
       </c>
-      <c r="E72" s="9">
-        <v>0</v>
-      </c>
-      <c r="F72" s="6">
+      <c r="E72" s="8">
+        <v>0</v>
+      </c>
+      <c r="F72" s="9">
         <f t="shared" ref="F72:F73" si="17">F71-D72+E72</f>
         <v>319204.25000000163</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="15" customHeight="1">
-      <c r="A73" s="15">
+      <c r="A73" s="4">
         <v>44973</v>
       </c>
-      <c r="B73" s="15">
+      <c r="B73" s="4">
         <v>44977</v>
       </c>
-      <c r="C73" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D73" s="8">
-        <v>14.98</v>
-      </c>
-      <c r="E73" s="8">
-        <v>0</v>
-      </c>
-      <c r="F73" s="6">
+      <c r="C73" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D73" s="6">
+        <v>14.98</v>
+      </c>
+      <c r="E73" s="6">
+        <v>0</v>
+      </c>
+      <c r="F73" s="9">
         <f t="shared" si="17"/>
         <v>319189.27000000165</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="15" customHeight="1">
-      <c r="A74" s="3">
+      <c r="A74" s="4">
         <v>44986</v>
       </c>
-      <c r="B74" s="3">
+      <c r="B74" s="4">
         <v>44988</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D74" s="9">
+      <c r="D74" s="8">
         <v>164364.64744000003</v>
       </c>
-      <c r="E74" s="9">
-        <v>0</v>
-      </c>
-      <c r="F74" s="6">
-        <f t="shared" ref="F74:F76" si="18">F73-D74+E74</f>
+      <c r="E74" s="8">
+        <v>0</v>
+      </c>
+      <c r="F74" s="9">
+        <f t="shared" ref="F74:F79" si="18">F73-D74+E74</f>
         <v>154824.62256000162</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="15" customHeight="1">
-      <c r="A75" s="3">
+      <c r="A75" s="4">
         <v>44986</v>
       </c>
-      <c r="B75" s="3">
+      <c r="B75" s="4">
         <v>44988</v>
       </c>
-      <c r="C75" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D75" s="8">
-        <v>14.98</v>
-      </c>
-      <c r="E75" s="8">
-        <v>0</v>
-      </c>
-      <c r="F75" s="6">
+      <c r="C75" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D75" s="6">
+        <v>14.98</v>
+      </c>
+      <c r="E75" s="6">
+        <v>0</v>
+      </c>
+      <c r="F75" s="9">
         <f t="shared" si="18"/>
         <v>154809.64256000161</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="15" customHeight="1">
-      <c r="A76" s="3" t="s">
+      <c r="A76" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B76" s="3">
+      <c r="B76" s="4">
         <v>44989</v>
       </c>
-      <c r="C76" s="7" t="s">
+      <c r="C76" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D76" s="8">
+      <c r="D76" s="6">
         <v>1320</v>
       </c>
-      <c r="E76" s="8">
-        <v>0</v>
-      </c>
-      <c r="F76" s="6">
+      <c r="E76" s="6">
+        <v>0</v>
+      </c>
+      <c r="F76" s="9">
         <f t="shared" si="18"/>
         <v>153489.64256000161</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="15" customHeight="1">
+      <c r="A77" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B77" s="4">
+        <v>44992</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D77" s="8">
+        <v>0</v>
+      </c>
+      <c r="E77" s="8">
+        <v>9126</v>
+      </c>
+      <c r="F77" s="9">
+        <f t="shared" si="18"/>
+        <v>162615.64256000161</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="15" customHeight="1">
+      <c r="A78" s="4">
+        <v>44992</v>
+      </c>
+      <c r="B78" s="4">
+        <v>44994</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D78" s="8">
+        <v>0</v>
+      </c>
+      <c r="E78" s="8">
+        <v>132705.42000000001</v>
+      </c>
+      <c r="F78" s="9">
+        <f t="shared" si="18"/>
+        <v>295321.06256000162</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="15" customHeight="1">
+      <c r="A79" s="4">
+        <v>44992</v>
+      </c>
+      <c r="B79" s="4">
+        <v>44994</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D79" s="6">
+        <v>14.98</v>
+      </c>
+      <c r="E79" s="6">
+        <v>0</v>
+      </c>
+      <c r="F79" s="9">
+        <f t="shared" si="18"/>
+        <v>295306.08256000164</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="15" customHeight="1">
+      <c r="A80" s="4">
+        <v>44993</v>
+      </c>
+      <c r="B80" s="4">
+        <v>44995</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D80" s="8">
+        <v>86591.37</v>
+      </c>
+      <c r="E80" s="8">
+        <v>0</v>
+      </c>
+      <c r="F80" s="9">
+        <f t="shared" ref="F80:F81" si="19">F79-D80+E80</f>
+        <v>208714.71256000164</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="15" customHeight="1">
+      <c r="A81" s="4">
+        <v>44993</v>
+      </c>
+      <c r="B81" s="4">
+        <v>44995</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D81" s="6">
+        <v>14.98</v>
+      </c>
+      <c r="E81" s="6">
+        <v>0</v>
+      </c>
+      <c r="F81" s="9">
+        <f t="shared" si="19"/>
+        <v>208699.73256000163</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="15" customHeight="1">
+      <c r="A82" s="4">
+        <v>44994</v>
+      </c>
+      <c r="B82" s="4">
+        <v>44998</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D82" s="8">
+        <v>70155.039999999994</v>
+      </c>
+      <c r="E82" s="8">
+        <v>0</v>
+      </c>
+      <c r="F82" s="9">
+        <f t="shared" ref="F82:F85" si="20">F81-D82+E82</f>
+        <v>138544.69256000163</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="15" customHeight="1">
+      <c r="A83" s="4">
+        <v>44994</v>
+      </c>
+      <c r="B83" s="4">
+        <v>44998</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D83" s="6">
+        <v>14.98</v>
+      </c>
+      <c r="E83" s="6">
+        <v>0</v>
+      </c>
+      <c r="F83" s="9">
+        <f t="shared" si="20"/>
+        <v>138529.71256000162</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="15" customHeight="1">
+      <c r="A84" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B84" s="4">
+        <v>44995</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D84" s="8">
+        <v>0</v>
+      </c>
+      <c r="E84" s="8">
+        <v>7128</v>
+      </c>
+      <c r="F84" s="9">
+        <f t="shared" si="20"/>
+        <v>145657.71256000162</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="15" customHeight="1">
+      <c r="A85" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B85" s="4">
+        <v>45233</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D85" s="6">
+        <v>20</v>
+      </c>
+      <c r="E85" s="6">
+        <v>0</v>
+      </c>
+      <c r="F85" s="9">
+        <f t="shared" si="20"/>
+        <v>145637.71256000162</v>
       </c>
     </row>
   </sheetData>
